--- a/AAII_Financials/Quarterly/TCOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TCOM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>TCOM</t>
   </si>
@@ -656,340 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1553000</v>
+        <v>1435400</v>
       </c>
       <c r="E8" s="3">
-        <v>1270100</v>
+        <v>1910100</v>
       </c>
       <c r="F8" s="3">
-        <v>694100</v>
+        <v>1563600</v>
       </c>
       <c r="G8" s="3">
-        <v>951600</v>
+        <v>1278700</v>
       </c>
       <c r="H8" s="3">
-        <v>553800</v>
+        <v>698900</v>
       </c>
       <c r="I8" s="3">
+        <v>958100</v>
+      </c>
+      <c r="J8" s="3">
+        <v>557600</v>
+      </c>
+      <c r="K8" s="3">
         <v>567400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>646400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>736300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>837300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>571800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>691000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>797600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>465500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>746400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1314900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1613100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1327800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1241900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1150000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1358600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1050100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>965800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>885700</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>277100</v>
+        <v>279400</v>
       </c>
       <c r="E9" s="3">
-        <v>226000</v>
+        <v>343000</v>
       </c>
       <c r="F9" s="3">
-        <v>165600</v>
+        <v>279000</v>
       </c>
       <c r="G9" s="3">
-        <v>175500</v>
+        <v>227600</v>
       </c>
       <c r="H9" s="3">
-        <v>134800</v>
+        <v>166700</v>
       </c>
       <c r="I9" s="3">
+        <v>176700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>135700</v>
+      </c>
+      <c r="K9" s="3">
         <v>147300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>154400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>168500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>173800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>143900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>126700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>150300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>128500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>192500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>272600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>332100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>274700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>256900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>246400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>289200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>210800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>178500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>152200</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1275900</v>
+        <v>1156000</v>
       </c>
       <c r="E10" s="3">
-        <v>1044000</v>
+        <v>1567200</v>
       </c>
       <c r="F10" s="3">
-        <v>528600</v>
+        <v>1284500</v>
       </c>
       <c r="G10" s="3">
-        <v>776100</v>
+        <v>1051100</v>
       </c>
       <c r="H10" s="3">
-        <v>419100</v>
+        <v>532200</v>
       </c>
       <c r="I10" s="3">
+        <v>781400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>421900</v>
+      </c>
+      <c r="K10" s="3">
         <v>420000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>492000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>567800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>663400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>427900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>564300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>647400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>337000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>553900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1042300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1281000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1053100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>985000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>903600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1069500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>839400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>787300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>733500</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,82 +1041,90 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>407800</v>
+        <v>405400</v>
       </c>
       <c r="E12" s="3">
-        <v>369200</v>
+        <v>497300</v>
       </c>
       <c r="F12" s="3">
-        <v>290500</v>
+        <v>410500</v>
       </c>
       <c r="G12" s="3">
-        <v>344000</v>
+        <v>371700</v>
       </c>
       <c r="H12" s="3">
-        <v>244700</v>
+        <v>292500</v>
       </c>
       <c r="I12" s="3">
+        <v>346300</v>
+      </c>
+      <c r="J12" s="3">
+        <v>246300</v>
+      </c>
+      <c r="K12" s="3">
         <v>272600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>308700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>317600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>316400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>309700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>301000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>293200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>265400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>267600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>425000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>429600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>403600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>387000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>413500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>361800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>323000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>309900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>297600</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1164,8 +1197,14 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1238,8 +1277,14 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1312,8 +1357,14 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1388,170 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1141900</v>
+        <v>1130000</v>
       </c>
       <c r="E17" s="3">
-        <v>960600</v>
+        <v>1366700</v>
       </c>
       <c r="F17" s="3">
-        <v>727300</v>
+        <v>1149700</v>
       </c>
       <c r="G17" s="3">
-        <v>833700</v>
+        <v>967200</v>
       </c>
       <c r="H17" s="3">
-        <v>576900</v>
+        <v>732200</v>
       </c>
       <c r="I17" s="3">
+        <v>839400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>580800</v>
+      </c>
+      <c r="K17" s="3">
         <v>616900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>743600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>770200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>790900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>681400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>693200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>682300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>566900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>984400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1223400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1267900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1124200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1107300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1178800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1143700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>946300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>881100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>842200</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>411100</v>
+        <v>305400</v>
       </c>
       <c r="E18" s="3">
-        <v>309400</v>
+        <v>543400</v>
       </c>
       <c r="F18" s="3">
-        <v>-33100</v>
+        <v>413900</v>
       </c>
       <c r="G18" s="3">
-        <v>117900</v>
+        <v>311500</v>
       </c>
       <c r="H18" s="3">
-        <v>-23100</v>
+        <v>-33400</v>
       </c>
       <c r="I18" s="3">
+        <v>118700</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-49600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-97200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-33900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>46300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-109600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>115400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-101400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-238100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>91500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>345200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>203700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>134600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-28800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>214900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>103900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>84700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>43500</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1513,82 +1578,90 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-199900</v>
+        <v>-43100</v>
       </c>
       <c r="E20" s="3">
-        <v>289000</v>
+        <v>151300</v>
       </c>
       <c r="F20" s="3">
-        <v>428900</v>
+        <v>-201300</v>
       </c>
       <c r="G20" s="3">
-        <v>8000</v>
+        <v>291000</v>
       </c>
       <c r="H20" s="3">
-        <v>139900</v>
+        <v>431800</v>
       </c>
       <c r="I20" s="3">
+        <v>8100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>140800</v>
+      </c>
+      <c r="K20" s="3">
         <v>-16000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-4700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>14200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-53400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>407300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>166800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>242600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>349100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-522800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>364600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-129300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-129900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>776300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-80500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-305600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>370200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>125800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>96600</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1634,14 +1707,14 @@
       <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R21" s="3">
-        <v>629000</v>
+      <c r="R21" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>16</v>
+      <c r="T21" s="3">
+        <v>629000</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>16</v>
@@ -1661,230 +1734,254 @@
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>76600</v>
+        <v>69100</v>
       </c>
       <c r="E22" s="3">
+        <v>73500</v>
+      </c>
+      <c r="F22" s="3">
+        <v>77200</v>
+      </c>
+      <c r="G22" s="3">
+        <v>67600</v>
+      </c>
+      <c r="H22" s="3">
+        <v>45900</v>
+      </c>
+      <c r="I22" s="3">
+        <v>68400</v>
+      </c>
+      <c r="J22" s="3">
+        <v>48800</v>
+      </c>
+      <c r="K22" s="3">
+        <v>47100</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" s="3">
+        <v>117700</v>
+      </c>
+      <c r="N22" s="3">
+        <v>59400</v>
+      </c>
+      <c r="O22" s="3">
+        <v>56700</v>
+      </c>
+      <c r="P22" s="3">
+        <v>52500</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>62800</v>
+      </c>
+      <c r="R22" s="3">
+        <v>67900</v>
+      </c>
+      <c r="S22" s="3">
+        <v>70700</v>
+      </c>
+      <c r="T22" s="3">
+        <v>61100</v>
+      </c>
+      <c r="U22" s="3">
+        <v>65100</v>
+      </c>
+      <c r="V22" s="3">
+        <v>65100</v>
+      </c>
+      <c r="W22" s="3">
         <v>67100</v>
       </c>
-      <c r="F22" s="3">
-        <v>45600</v>
-      </c>
-      <c r="G22" s="3">
-        <v>67900</v>
-      </c>
-      <c r="H22" s="3">
-        <v>48500</v>
-      </c>
-      <c r="I22" s="3">
-        <v>47100</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K22" s="3">
-        <v>117700</v>
-      </c>
-      <c r="L22" s="3">
-        <v>59400</v>
-      </c>
-      <c r="M22" s="3">
-        <v>56700</v>
-      </c>
-      <c r="N22" s="3">
-        <v>52500</v>
-      </c>
-      <c r="O22" s="3">
-        <v>62800</v>
-      </c>
-      <c r="P22" s="3">
-        <v>67900</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>70700</v>
-      </c>
-      <c r="R22" s="3">
-        <v>61100</v>
-      </c>
-      <c r="S22" s="3">
-        <v>65100</v>
-      </c>
-      <c r="T22" s="3">
-        <v>65100</v>
-      </c>
-      <c r="U22" s="3">
-        <v>67100</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>64200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>57100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>53200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>46200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>134500</v>
+        <v>193200</v>
       </c>
       <c r="E23" s="3">
-        <v>531300</v>
+        <v>621100</v>
       </c>
       <c r="F23" s="3">
-        <v>350200</v>
+        <v>135400</v>
       </c>
       <c r="G23" s="3">
-        <v>58000</v>
+        <v>534900</v>
       </c>
       <c r="H23" s="3">
-        <v>68300</v>
+        <v>352600</v>
       </c>
       <c r="I23" s="3">
+        <v>58400</v>
+      </c>
+      <c r="J23" s="3">
+        <v>68800</v>
+      </c>
+      <c r="K23" s="3">
         <v>-112700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-101900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-137400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-66500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>241100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>112100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>295100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>179800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-831600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>395000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>150700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>8700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>843800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-173400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-147700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>420800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>164300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>93500</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>77600</v>
+        <v>55500</v>
       </c>
       <c r="E24" s="3">
-        <v>47100</v>
+        <v>62300</v>
       </c>
       <c r="F24" s="3">
-        <v>34000</v>
+        <v>78100</v>
       </c>
       <c r="G24" s="3">
-        <v>38200</v>
+        <v>47400</v>
       </c>
       <c r="H24" s="3">
-        <v>23900</v>
+        <v>34200</v>
       </c>
       <c r="I24" s="3">
+        <v>38500</v>
+      </c>
+      <c r="J24" s="3">
+        <v>24100</v>
+      </c>
+      <c r="K24" s="3">
         <v>-1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>5100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>13100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>13800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>5700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>22700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>35800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>29600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-40100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>57400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>56200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>51300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>103000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>5300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>37300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>46200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>25700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2054,174 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>56900</v>
+        <v>137800</v>
       </c>
       <c r="E26" s="3">
-        <v>484200</v>
+        <v>558900</v>
       </c>
       <c r="F26" s="3">
-        <v>316200</v>
+        <v>57300</v>
       </c>
       <c r="G26" s="3">
-        <v>19700</v>
+        <v>487500</v>
       </c>
       <c r="H26" s="3">
-        <v>44500</v>
+        <v>318400</v>
       </c>
       <c r="I26" s="3">
+        <v>19900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>44800</v>
+      </c>
+      <c r="K26" s="3">
         <v>-110700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-107000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-150500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-80300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>235400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>89400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>259300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>150200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-791500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>337600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>94500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-42600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>740800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-178700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-185000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>374600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>138600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>87100</v>
+        <v>180300</v>
       </c>
       <c r="E27" s="3">
-        <v>466000</v>
+        <v>641600</v>
       </c>
       <c r="F27" s="3">
-        <v>284000</v>
+        <v>87700</v>
       </c>
       <c r="G27" s="3">
-        <v>36700</v>
+        <v>469200</v>
       </c>
       <c r="H27" s="3">
-        <v>9500</v>
+        <v>286000</v>
       </c>
       <c r="I27" s="3">
+        <v>37000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>9600</v>
+      </c>
+      <c r="K27" s="3">
         <v>-136600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-115200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-117000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-92000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>247800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>139800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>230400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-70100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-844500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>316800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>122100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-61600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>701700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-181000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-165400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>341600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>152100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2294,14 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2374,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2454,14 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2534,174 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>199900</v>
+        <v>43100</v>
       </c>
       <c r="E32" s="3">
-        <v>-289000</v>
+        <v>-151300</v>
       </c>
       <c r="F32" s="3">
-        <v>-428900</v>
+        <v>201300</v>
       </c>
       <c r="G32" s="3">
-        <v>-8000</v>
+        <v>-291000</v>
       </c>
       <c r="H32" s="3">
-        <v>-139900</v>
+        <v>-431800</v>
       </c>
       <c r="I32" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-140800</v>
+      </c>
+      <c r="K32" s="3">
         <v>16000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>4700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-14200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>53400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-407300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-166800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-242600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-349100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>522800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-364600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>129300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>129900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-776300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>80500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>305600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-370200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-125800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-96600</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>87100</v>
+        <v>180300</v>
       </c>
       <c r="E33" s="3">
-        <v>466000</v>
+        <v>641600</v>
       </c>
       <c r="F33" s="3">
-        <v>284000</v>
+        <v>87700</v>
       </c>
       <c r="G33" s="3">
-        <v>36700</v>
+        <v>469200</v>
       </c>
       <c r="H33" s="3">
-        <v>9500</v>
+        <v>286000</v>
       </c>
       <c r="I33" s="3">
+        <v>37000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>9600</v>
+      </c>
+      <c r="K33" s="3">
         <v>-136600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-115200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-117000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-92000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>247800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>139800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>230400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-70100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-844500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>316800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>122100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-61600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>701700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-181000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-165400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>341600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>152100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2774,179 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>87100</v>
+        <v>180300</v>
       </c>
       <c r="E35" s="3">
-        <v>466000</v>
+        <v>641600</v>
       </c>
       <c r="F35" s="3">
-        <v>284000</v>
+        <v>87700</v>
       </c>
       <c r="G35" s="3">
-        <v>36700</v>
+        <v>469200</v>
       </c>
       <c r="H35" s="3">
-        <v>9500</v>
+        <v>286000</v>
       </c>
       <c r="I35" s="3">
+        <v>37000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>9600</v>
+      </c>
+      <c r="K35" s="3">
         <v>-136600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-115200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-117000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-92000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>247800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>139800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>230400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-70100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-844500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>316800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>122100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-61600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>701700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-181000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-165400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>341600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>152100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2973,10 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,230 +3003,250 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5087300</v>
+        <v>6114500</v>
       </c>
       <c r="E41" s="3">
-        <v>4221900</v>
+        <v>5249500</v>
       </c>
       <c r="F41" s="3">
-        <v>2347400</v>
+        <v>5121900</v>
       </c>
       <c r="G41" s="3">
-        <v>2611900</v>
+        <v>4250700</v>
       </c>
       <c r="H41" s="3">
-        <v>3170200</v>
+        <v>2363300</v>
       </c>
       <c r="I41" s="3">
+        <v>2629700</v>
+      </c>
+      <c r="J41" s="3">
+        <v>3191800</v>
+      </c>
+      <c r="K41" s="3">
         <v>2880500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2736500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2828300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3937000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3210000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2519000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3680700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2784500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3800900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3143100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2822500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>3514200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3454300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>3275100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>3121000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>3162400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2475500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2617500</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2558900</v>
+        <v>2467300</v>
       </c>
       <c r="E42" s="3">
-        <v>2400700</v>
+        <v>3347000</v>
       </c>
       <c r="F42" s="3">
-        <v>3527300</v>
+        <v>2576300</v>
       </c>
       <c r="G42" s="3">
-        <v>3960700</v>
+        <v>2417000</v>
       </c>
       <c r="H42" s="3">
-        <v>4242000</v>
+        <v>3551300</v>
       </c>
       <c r="I42" s="3">
+        <v>3987600</v>
+      </c>
+      <c r="J42" s="3">
+        <v>4270800</v>
+      </c>
+      <c r="K42" s="3">
         <v>4193400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>4082500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>5081700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>5015900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>4270500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>3454900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>3245400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>3519800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>3955500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>3637600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>4014100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>5033900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>5126900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>5590900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>5488700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>4760400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>4896000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>4036100</v>
       </c>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1475900</v>
+        <v>1586200</v>
       </c>
       <c r="E43" s="3">
-        <v>1278200</v>
+        <v>1785700</v>
       </c>
       <c r="F43" s="3">
-        <v>998900</v>
+        <v>1486000</v>
       </c>
       <c r="G43" s="3">
-        <v>849300</v>
+        <v>1286900</v>
       </c>
       <c r="H43" s="3">
-        <v>751800</v>
+        <v>1005700</v>
       </c>
       <c r="I43" s="3">
+        <v>855100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>757000</v>
+      </c>
+      <c r="K43" s="3">
         <v>549400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>871800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>718200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>758900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>605900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>824200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>844600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>755800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>804300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1647000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1431200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1577500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>929100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1112000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>987100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>898300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>742900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>735000</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3128,378 +3319,414 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2351200</v>
+        <v>2167500</v>
       </c>
       <c r="E45" s="3">
-        <v>2094300</v>
+        <v>2631200</v>
       </c>
       <c r="F45" s="3">
-        <v>1609500</v>
+        <v>2367200</v>
       </c>
       <c r="G45" s="3">
-        <v>1835600</v>
+        <v>2108500</v>
       </c>
       <c r="H45" s="3">
-        <v>1488200</v>
+        <v>1620400</v>
       </c>
       <c r="I45" s="3">
+        <v>1848100</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1498400</v>
+      </c>
+      <c r="K45" s="3">
         <v>1280600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1437400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1925100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1475100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1362200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1277000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1835500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2296300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1638200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>2292900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>3369700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>2122000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>2560200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>2099400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>2669900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1838400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1400500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1190300</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>11473300</v>
+        <v>12335500</v>
       </c>
       <c r="E46" s="3">
-        <v>9995100</v>
+        <v>13013500</v>
       </c>
       <c r="F46" s="3">
-        <v>8482900</v>
+        <v>11551400</v>
       </c>
       <c r="G46" s="3">
-        <v>9257600</v>
+        <v>10063100</v>
       </c>
       <c r="H46" s="3">
-        <v>9652200</v>
+        <v>8540700</v>
       </c>
       <c r="I46" s="3">
+        <v>9320600</v>
+      </c>
+      <c r="J46" s="3">
+        <v>9717900</v>
+      </c>
+      <c r="K46" s="3">
         <v>8903800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>9128200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10553400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>11186900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>9448600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>8075100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>9606100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>9356500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>10198900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>10720600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>11637500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>12247600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>12070600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>12077400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>12266700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>10659600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>9514900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>8525300</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>7560800</v>
+        <v>6859500</v>
       </c>
       <c r="E47" s="3">
-        <v>7831900</v>
+        <v>7432700</v>
       </c>
       <c r="F47" s="3">
-        <v>6931900</v>
+        <v>7612300</v>
       </c>
       <c r="G47" s="3">
-        <v>6490300</v>
+        <v>7885200</v>
       </c>
       <c r="H47" s="3">
-        <v>6085900</v>
+        <v>6979100</v>
       </c>
       <c r="I47" s="3">
+        <v>6534500</v>
+      </c>
+      <c r="J47" s="3">
+        <v>6127300</v>
+      </c>
+      <c r="K47" s="3">
         <v>5891600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>6211700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>5954300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>6686600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>6715800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>6677100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>7448000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>7907200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>8101400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>8096900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>7340700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>5350800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>5212700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>4122900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>3724400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>3907000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>3652100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>3737400</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>815600</v>
+        <v>804000</v>
       </c>
       <c r="E48" s="3">
-        <v>814300</v>
+        <v>809000</v>
       </c>
       <c r="F48" s="3">
-        <v>831700</v>
+        <v>821200</v>
       </c>
       <c r="G48" s="3">
-        <v>841600</v>
+        <v>819800</v>
       </c>
       <c r="H48" s="3">
-        <v>860500</v>
+        <v>837300</v>
       </c>
       <c r="I48" s="3">
+        <v>847300</v>
+      </c>
+      <c r="J48" s="3">
+        <v>866400</v>
+      </c>
+      <c r="K48" s="3">
         <v>841700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>871400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>888100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>940900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>949500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>942000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>973700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>999100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1145700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1158300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1073400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1059800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1013900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>893200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>847700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>835300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>830000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>805800</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9958300</v>
+        <v>10011700</v>
       </c>
       <c r="E49" s="3">
-        <v>9958500</v>
+        <v>10016900</v>
       </c>
       <c r="F49" s="3">
-        <v>9964100</v>
+        <v>10026100</v>
       </c>
       <c r="G49" s="3">
-        <v>9966900</v>
+        <v>10026300</v>
       </c>
       <c r="H49" s="3">
-        <v>9977000</v>
+        <v>10032000</v>
       </c>
       <c r="I49" s="3">
+        <v>10034700</v>
+      </c>
+      <c r="J49" s="3">
+        <v>10044900</v>
+      </c>
+      <c r="K49" s="3">
         <v>9989300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>9996900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>9984200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>10310100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>10103600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>10119400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>10649200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>10705900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>11274500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>11291200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>10976900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>10908600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>10878900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>10928800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>10452200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>10276000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>10086500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>10056900</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3799,14 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,82 +3879,94 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>323100</v>
+        <v>453800</v>
       </c>
       <c r="E52" s="3">
-        <v>277400</v>
+        <v>356600</v>
       </c>
       <c r="F52" s="3">
-        <v>258100</v>
+        <v>325300</v>
       </c>
       <c r="G52" s="3">
-        <v>272300</v>
+        <v>279300</v>
       </c>
       <c r="H52" s="3">
-        <v>298700</v>
+        <v>259800</v>
       </c>
       <c r="I52" s="3">
+        <v>274100</v>
+      </c>
+      <c r="J52" s="3">
+        <v>300700</v>
+      </c>
+      <c r="K52" s="3">
         <v>307500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>283800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>295000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>301200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>266400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>251400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>265900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>281600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>311100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>311700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>242200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>266800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>217700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>246100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>211200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>240300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>190500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>186800</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +4039,94 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>30131300</v>
+        <v>30464400</v>
       </c>
       <c r="E54" s="3">
-        <v>28877100</v>
+        <v>31628700</v>
       </c>
       <c r="F54" s="3">
-        <v>26468700</v>
+        <v>30336400</v>
       </c>
       <c r="G54" s="3">
-        <v>26828700</v>
+        <v>29073700</v>
       </c>
       <c r="H54" s="3">
-        <v>26874200</v>
+        <v>26648900</v>
       </c>
       <c r="I54" s="3">
+        <v>27011300</v>
+      </c>
+      <c r="J54" s="3">
+        <v>27057200</v>
+      </c>
+      <c r="K54" s="3">
         <v>25933900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>26491900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>27675000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>29425800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>27483900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>26065100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>28943000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>29250200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>31031500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>31578700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>31270700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>29833700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>29393700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>28268500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>27502200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>25918200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>24274100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>23278200</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4153,10 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,452 +4183,490 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2033800</v>
+        <v>2288100</v>
       </c>
       <c r="E57" s="3">
-        <v>1558500</v>
+        <v>2526400</v>
       </c>
       <c r="F57" s="3">
-        <v>1045100</v>
+        <v>2047600</v>
       </c>
       <c r="G57" s="3">
-        <v>1020300</v>
+        <v>1569100</v>
       </c>
       <c r="H57" s="3">
-        <v>931300</v>
+        <v>1052200</v>
       </c>
       <c r="I57" s="3">
+        <v>1027200</v>
+      </c>
+      <c r="J57" s="3">
+        <v>937700</v>
+      </c>
+      <c r="K57" s="3">
         <v>580100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>831100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1009200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>934900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>692200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>627200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1038100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>659900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>777600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1939500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2061200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1974700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1668600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1781900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1975000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1593800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1351000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1070200</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4475700</v>
+        <v>3594600</v>
       </c>
       <c r="E58" s="3">
-        <v>5417000</v>
+        <v>4282800</v>
       </c>
       <c r="F58" s="3">
-        <v>4511600</v>
+        <v>4506200</v>
       </c>
       <c r="G58" s="3">
-        <v>4676500</v>
+        <v>5453900</v>
       </c>
       <c r="H58" s="3">
-        <v>4998900</v>
+        <v>4542300</v>
       </c>
       <c r="I58" s="3">
+        <v>4708300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>5032900</v>
+      </c>
+      <c r="K58" s="3">
         <v>4262500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>5504700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>6219800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>5823500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>5678800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>4686200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>5012900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>6203400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>6370700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>4814200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>5658900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>5758300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>5769000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>5478000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>5232100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3509800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>2952200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>2341000</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3940000</v>
+        <v>4183800</v>
       </c>
       <c r="E59" s="3">
-        <v>3317900</v>
+        <v>4278800</v>
       </c>
       <c r="F59" s="3">
-        <v>2899100</v>
+        <v>3966800</v>
       </c>
       <c r="G59" s="3">
-        <v>2823900</v>
+        <v>3340500</v>
       </c>
       <c r="H59" s="3">
-        <v>2726800</v>
+        <v>2918900</v>
       </c>
       <c r="I59" s="3">
+        <v>2843100</v>
+      </c>
+      <c r="J59" s="3">
+        <v>2745400</v>
+      </c>
+      <c r="K59" s="3">
         <v>2588300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2807600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2900100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2988800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2765800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2811600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2909400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2944500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3547900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>4160400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>3692600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>3668900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>3135500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>3203500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2823300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>2821200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>2478900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>2698200</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10449500</v>
+        <v>10066600</v>
       </c>
       <c r="E60" s="3">
-        <v>10293400</v>
+        <v>11088000</v>
       </c>
       <c r="F60" s="3">
-        <v>8455900</v>
+        <v>10520600</v>
       </c>
       <c r="G60" s="3">
-        <v>8520600</v>
+        <v>10363500</v>
       </c>
       <c r="H60" s="3">
-        <v>8657100</v>
+        <v>8513400</v>
       </c>
       <c r="I60" s="3">
+        <v>8578600</v>
+      </c>
+      <c r="J60" s="3">
+        <v>8716000</v>
+      </c>
+      <c r="K60" s="3">
         <v>7430900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>9143400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>10129200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>9747200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>9136800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>8125000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>8960400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>9807800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>10696100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>10914200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>11412700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>11401800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>10573100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>10463400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>10030300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>7924800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>6782200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>6049400</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2719800</v>
+        <v>2655100</v>
       </c>
       <c r="E61" s="3">
-        <v>1857600</v>
+        <v>2735500</v>
       </c>
       <c r="F61" s="3">
-        <v>1819500</v>
+        <v>2738300</v>
       </c>
       <c r="G61" s="3">
-        <v>2407400</v>
+        <v>1870200</v>
       </c>
       <c r="H61" s="3">
-        <v>2402900</v>
+        <v>1831900</v>
       </c>
       <c r="I61" s="3">
+        <v>2423800</v>
+      </c>
+      <c r="J61" s="3">
+        <v>2419200</v>
+      </c>
+      <c r="K61" s="3">
         <v>2803300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1531700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1690700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3228700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3251200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3162300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>4710800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>4136000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>3674500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>3082200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>3172000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>3311200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>3721600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>3673100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>3785000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>4291800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>4171300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>4192500</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>613200</v>
+        <v>642400</v>
       </c>
       <c r="E62" s="3">
-        <v>586300</v>
+        <v>620700</v>
       </c>
       <c r="F62" s="3">
-        <v>587700</v>
+        <v>617400</v>
       </c>
       <c r="G62" s="3">
-        <v>581600</v>
+        <v>590300</v>
       </c>
       <c r="H62" s="3">
-        <v>587100</v>
+        <v>591700</v>
       </c>
       <c r="I62" s="3">
+        <v>585600</v>
+      </c>
+      <c r="J62" s="3">
+        <v>591100</v>
+      </c>
+      <c r="K62" s="3">
         <v>555800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>565000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>571400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>624300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>649400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>639600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>627800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>635000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>725400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>726500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>698100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>683800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>748700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>633900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>618100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>649800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>592000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>608800</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4739,14 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4819,14 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4899,94 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13886300</v>
+        <v>13478400</v>
       </c>
       <c r="E66" s="3">
-        <v>12839100</v>
+        <v>14554100</v>
       </c>
       <c r="F66" s="3">
-        <v>10964700</v>
+        <v>13980800</v>
       </c>
       <c r="G66" s="3">
-        <v>11608100</v>
+        <v>12926500</v>
       </c>
       <c r="H66" s="3">
-        <v>11748700</v>
+        <v>11039300</v>
       </c>
       <c r="I66" s="3">
+        <v>11687100</v>
+      </c>
+      <c r="J66" s="3">
+        <v>11828700</v>
+      </c>
+      <c r="K66" s="3">
         <v>10895200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>11347700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>12518600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>13733100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>13169000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>12095800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>14527600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>14878300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>15631500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>15259700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>15770800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>15766100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>15412600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>15077400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>14757400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>13139500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>11814400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>11105900</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +5013,10 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +5089,14 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5169,14 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5249,14 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,8 +5329,14 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4999,71 +5346,77 @@
       <c r="E72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F72" s="3">
-        <v>2894200</v>
+      <c r="F72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>16</v>
+      <c r="H72" s="3">
+        <v>2913900</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J72" s="3">
-        <v>2700400</v>
+      <c r="J72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>16</v>
+      <c r="L72" s="3">
+        <v>2700400</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N72" s="3">
-        <v>2798900</v>
+      <c r="N72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>16</v>
+      <c r="P72" s="3">
+        <v>2798900</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R72" s="3">
-        <v>3697600</v>
+      <c r="R72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="T72" s="3">
-        <v>3152900</v>
+        <v>3697600</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="V72" s="3">
-        <v>2498900</v>
+        <v>3152900</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X72" s="3" t="s">
+      <c r="X72" s="3">
+        <v>2498900</v>
+      </c>
+      <c r="Y72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA72" s="3">
         <v>2379000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>2227000</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5489,14 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5569,14 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5649,94 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>16245000</v>
+        <v>16986000</v>
       </c>
       <c r="E76" s="3">
-        <v>16038000</v>
+        <v>17074600</v>
       </c>
       <c r="F76" s="3">
-        <v>15504000</v>
+        <v>16355600</v>
       </c>
       <c r="G76" s="3">
-        <v>15220600</v>
+        <v>16147200</v>
       </c>
       <c r="H76" s="3">
-        <v>15125600</v>
+        <v>15609600</v>
       </c>
       <c r="I76" s="3">
+        <v>15324200</v>
+      </c>
+      <c r="J76" s="3">
+        <v>15228500</v>
+      </c>
+      <c r="K76" s="3">
         <v>15038700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>15144200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>15156500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>15692600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>14314900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>13969300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>14415400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>14371900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>15400100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>16319000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>15499900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>14067500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>13981000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>13191100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>12744800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>12778800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>12459700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>12172300</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5809,179 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>87100</v>
+        <v>180300</v>
       </c>
       <c r="E81" s="3">
-        <v>466000</v>
+        <v>641600</v>
       </c>
       <c r="F81" s="3">
-        <v>284000</v>
+        <v>87700</v>
       </c>
       <c r="G81" s="3">
-        <v>36700</v>
+        <v>469200</v>
       </c>
       <c r="H81" s="3">
-        <v>9500</v>
+        <v>286000</v>
       </c>
       <c r="I81" s="3">
+        <v>37000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>9600</v>
+      </c>
+      <c r="K81" s="3">
         <v>-136600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-115200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-117000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-92000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>247800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>139800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>230400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-70100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-844500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>316800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>122100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-61600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>701700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-181000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-165400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>341600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>152100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +6008,10 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5657,18 +6054,18 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>172900</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
@@ -5687,8 +6084,14 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +6164,14 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6244,14 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6324,14 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6404,14 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,8 +6484,14 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6101,18 +6534,18 @@
       <c r="P89" s="3">
         <v>0</v>
       </c>
-      <c r="Q89" s="3" t="s">
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1156900</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
@@ -6131,8 +6564,14 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,8 +6598,10 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6203,18 +6644,18 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-129800</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
@@ -6233,8 +6674,14 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6754,14 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,8 +6834,14 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6425,18 +6884,18 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-380700</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
@@ -6455,8 +6914,14 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6948,10 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6557,8 +7024,14 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +7104,14 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +7184,14 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,8 +7264,14 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6823,18 +7314,18 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-      <c r="Q100" s="3" t="s">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1460200</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
@@ -6853,8 +7344,14 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6897,18 +7394,18 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>48700</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
@@ -6927,8 +7424,14 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6971,18 +7474,18 @@
       <c r="P102" s="3">
         <v>0</v>
       </c>
-      <c r="Q102" s="3" t="s">
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-635300</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
         <v>0</v>
       </c>
@@ -6999,6 +7502,12 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TCOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TCOM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>TCOM</t>
   </si>
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1435400</v>
+        <v>1644800</v>
       </c>
       <c r="E8" s="3">
-        <v>1910100</v>
+        <v>1426500</v>
       </c>
       <c r="F8" s="3">
-        <v>1563600</v>
+        <v>1898300</v>
       </c>
       <c r="G8" s="3">
-        <v>1278700</v>
+        <v>1553900</v>
       </c>
       <c r="H8" s="3">
-        <v>698900</v>
+        <v>1270800</v>
       </c>
       <c r="I8" s="3">
-        <v>958100</v>
+        <v>694500</v>
       </c>
       <c r="J8" s="3">
+        <v>952200</v>
+      </c>
+      <c r="K8" s="3">
         <v>557600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>567400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>646400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>736300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>837300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>571800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>691000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>797600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>465500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>746400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1314900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1613100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1327800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1241900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1150000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1358600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1050100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>965800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>885700</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>279400</v>
+        <v>309200</v>
       </c>
       <c r="E9" s="3">
-        <v>343000</v>
+        <v>277700</v>
       </c>
       <c r="F9" s="3">
-        <v>279000</v>
+        <v>340800</v>
       </c>
       <c r="G9" s="3">
-        <v>227600</v>
+        <v>277300</v>
       </c>
       <c r="H9" s="3">
-        <v>166700</v>
+        <v>226200</v>
       </c>
       <c r="I9" s="3">
-        <v>176700</v>
+        <v>165700</v>
       </c>
       <c r="J9" s="3">
+        <v>175600</v>
+      </c>
+      <c r="K9" s="3">
         <v>135700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>147300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>154400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>168500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>173800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>143900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>126700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>150300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>128500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>192500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>272600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>332100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>274700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>256900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>246400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>289200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>210800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>178500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>152200</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1156000</v>
+        <v>1335600</v>
       </c>
       <c r="E10" s="3">
-        <v>1567200</v>
+        <v>1148800</v>
       </c>
       <c r="F10" s="3">
-        <v>1284500</v>
+        <v>1557500</v>
       </c>
       <c r="G10" s="3">
-        <v>1051100</v>
+        <v>1276600</v>
       </c>
       <c r="H10" s="3">
-        <v>532200</v>
+        <v>1044600</v>
       </c>
       <c r="I10" s="3">
-        <v>781400</v>
+        <v>528900</v>
       </c>
       <c r="J10" s="3">
+        <v>776600</v>
+      </c>
+      <c r="K10" s="3">
         <v>421900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>420000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>492000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>567800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>663400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>427900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>564300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>647400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>337000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>553900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1042300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1281000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1053100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>985000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>903600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1069500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>839400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>787300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>733500</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,88 +1056,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>405400</v>
+        <v>429500</v>
       </c>
       <c r="E12" s="3">
-        <v>497300</v>
+        <v>402900</v>
       </c>
       <c r="F12" s="3">
-        <v>410500</v>
+        <v>494200</v>
       </c>
       <c r="G12" s="3">
-        <v>371700</v>
+        <v>408000</v>
       </c>
       <c r="H12" s="3">
-        <v>292500</v>
+        <v>369400</v>
       </c>
       <c r="I12" s="3">
-        <v>346300</v>
+        <v>290700</v>
       </c>
       <c r="J12" s="3">
+        <v>344200</v>
+      </c>
+      <c r="K12" s="3">
         <v>246300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>272600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>308700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>317600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>316400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>309700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>301000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>293200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>265400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>267600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>425000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>429600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>403600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>387000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>413500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>361800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>323000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>309900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>297600</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1203,8 +1220,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1283,8 +1303,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1130000</v>
+        <v>1186800</v>
       </c>
       <c r="E17" s="3">
-        <v>1366700</v>
+        <v>1123000</v>
       </c>
       <c r="F17" s="3">
-        <v>1149700</v>
+        <v>1358300</v>
       </c>
       <c r="G17" s="3">
-        <v>967200</v>
+        <v>1142600</v>
       </c>
       <c r="H17" s="3">
-        <v>732200</v>
+        <v>961200</v>
       </c>
       <c r="I17" s="3">
-        <v>839400</v>
+        <v>727700</v>
       </c>
       <c r="J17" s="3">
+        <v>834200</v>
+      </c>
+      <c r="K17" s="3">
         <v>580800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>616900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>743600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>770200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>790900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>681400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>693200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>682300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>566900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>984400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1223400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1267900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1124200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1107300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1178800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1143700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>946300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>881100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>842200</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>305400</v>
+        <v>458000</v>
       </c>
       <c r="E18" s="3">
-        <v>543400</v>
+        <v>303500</v>
       </c>
       <c r="F18" s="3">
-        <v>413900</v>
+        <v>540100</v>
       </c>
       <c r="G18" s="3">
-        <v>311500</v>
+        <v>411300</v>
       </c>
       <c r="H18" s="3">
-        <v>-33400</v>
+        <v>309600</v>
       </c>
       <c r="I18" s="3">
-        <v>118700</v>
+        <v>-33200</v>
       </c>
       <c r="J18" s="3">
+        <v>118000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-23200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-49600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-97200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-33900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>46300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-109600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>115400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-101400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-238100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>91500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>345200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>203700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>134600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-28800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>214900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>103900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>84700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>43500</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1580,88 +1613,92 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-43100</v>
+        <v>186700</v>
       </c>
       <c r="E20" s="3">
-        <v>151300</v>
+        <v>-42800</v>
       </c>
       <c r="F20" s="3">
-        <v>-201300</v>
+        <v>150300</v>
       </c>
       <c r="G20" s="3">
-        <v>291000</v>
+        <v>-200100</v>
       </c>
       <c r="H20" s="3">
-        <v>431800</v>
+        <v>289200</v>
       </c>
       <c r="I20" s="3">
-        <v>8100</v>
+        <v>429100</v>
       </c>
       <c r="J20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K20" s="3">
         <v>140800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-16000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-53400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>407300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>166800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>242600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>349100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-522800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>364600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-129300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-129900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>776300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-80500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-305600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>370200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>125800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>96600</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1713,11 +1750,11 @@
       <c r="S21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U21" s="3">
         <v>629000</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>16</v>
@@ -1740,248 +1777,260 @@
       <c r="AB21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>69100</v>
+        <v>68900</v>
       </c>
       <c r="E22" s="3">
-        <v>73500</v>
+        <v>68700</v>
       </c>
       <c r="F22" s="3">
-        <v>77200</v>
+        <v>73100</v>
       </c>
       <c r="G22" s="3">
-        <v>67600</v>
+        <v>76700</v>
       </c>
       <c r="H22" s="3">
-        <v>45900</v>
+        <v>67100</v>
       </c>
       <c r="I22" s="3">
-        <v>68400</v>
+        <v>45600</v>
       </c>
       <c r="J22" s="3">
+        <v>68000</v>
+      </c>
+      <c r="K22" s="3">
         <v>48800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>47100</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>117700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>59400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>56700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>52500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>62800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>67900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>70700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>61100</v>
-      </c>
-      <c r="U22" s="3">
-        <v>65100</v>
       </c>
       <c r="V22" s="3">
         <v>65100</v>
       </c>
       <c r="W22" s="3">
+        <v>65100</v>
+      </c>
+      <c r="X22" s="3">
         <v>67100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>64200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>57100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>53200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>46200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>193200</v>
+        <v>575700</v>
       </c>
       <c r="E23" s="3">
-        <v>621100</v>
+        <v>192000</v>
       </c>
       <c r="F23" s="3">
-        <v>135400</v>
+        <v>617300</v>
       </c>
       <c r="G23" s="3">
-        <v>534900</v>
+        <v>134600</v>
       </c>
       <c r="H23" s="3">
-        <v>352600</v>
+        <v>531600</v>
       </c>
       <c r="I23" s="3">
-        <v>58400</v>
+        <v>350400</v>
       </c>
       <c r="J23" s="3">
+        <v>58000</v>
+      </c>
+      <c r="K23" s="3">
         <v>68800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-112700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-101900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-137400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-66500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>241100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>112100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>295100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>179800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-831600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>395000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>150700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>843800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-173400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-147700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>420800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>164300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>93500</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>55500</v>
+        <v>91700</v>
       </c>
       <c r="E24" s="3">
-        <v>62300</v>
+        <v>55100</v>
       </c>
       <c r="F24" s="3">
-        <v>78100</v>
+        <v>61900</v>
       </c>
       <c r="G24" s="3">
-        <v>47400</v>
+        <v>77600</v>
       </c>
       <c r="H24" s="3">
-        <v>34200</v>
+        <v>47100</v>
       </c>
       <c r="I24" s="3">
-        <v>38500</v>
+        <v>34000</v>
       </c>
       <c r="J24" s="3">
+        <v>38300</v>
+      </c>
+      <c r="K24" s="3">
         <v>24100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>13100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>13800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>22700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>35800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>29600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-40100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>57400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>56200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>51300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>103000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>37300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>46200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>25700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>137800</v>
+        <v>484000</v>
       </c>
       <c r="E26" s="3">
-        <v>558900</v>
+        <v>136900</v>
       </c>
       <c r="F26" s="3">
-        <v>57300</v>
+        <v>555400</v>
       </c>
       <c r="G26" s="3">
-        <v>487500</v>
+        <v>56900</v>
       </c>
       <c r="H26" s="3">
-        <v>318400</v>
+        <v>484500</v>
       </c>
       <c r="I26" s="3">
-        <v>19900</v>
+        <v>316400</v>
       </c>
       <c r="J26" s="3">
+        <v>19800</v>
+      </c>
+      <c r="K26" s="3">
         <v>44800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-110700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-107000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-150500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-80300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>235400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>89400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>259300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>150200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-791500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>337600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>94500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-42600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>740800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-178700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-185000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>374600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>138600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>180300</v>
+        <v>595700</v>
       </c>
       <c r="E27" s="3">
-        <v>641600</v>
+        <v>179300</v>
       </c>
       <c r="F27" s="3">
-        <v>87700</v>
+        <v>637600</v>
       </c>
       <c r="G27" s="3">
-        <v>469200</v>
+        <v>87200</v>
       </c>
       <c r="H27" s="3">
-        <v>286000</v>
+        <v>466300</v>
       </c>
       <c r="I27" s="3">
-        <v>37000</v>
+        <v>284200</v>
       </c>
       <c r="J27" s="3">
+        <v>36800</v>
+      </c>
+      <c r="K27" s="3">
         <v>9600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-136600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-115200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-117000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-92000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>247800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>139800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>230400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-70100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-844500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>316800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>122100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-61600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>701700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-181000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-165400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>341600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>152100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2607,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>43100</v>
+        <v>-186700</v>
       </c>
       <c r="E32" s="3">
-        <v>-151300</v>
+        <v>42800</v>
       </c>
       <c r="F32" s="3">
-        <v>201300</v>
+        <v>-150300</v>
       </c>
       <c r="G32" s="3">
-        <v>-291000</v>
+        <v>200100</v>
       </c>
       <c r="H32" s="3">
-        <v>-431800</v>
+        <v>-289200</v>
       </c>
       <c r="I32" s="3">
-        <v>-8100</v>
+        <v>-429100</v>
       </c>
       <c r="J32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-140800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>16000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>53400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-407300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-166800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-242600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-349100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>522800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-364600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>129300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>129900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-776300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>80500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>305600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-370200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-125800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-96600</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>180300</v>
+        <v>595700</v>
       </c>
       <c r="E33" s="3">
-        <v>641600</v>
+        <v>179300</v>
       </c>
       <c r="F33" s="3">
-        <v>87700</v>
+        <v>637600</v>
       </c>
       <c r="G33" s="3">
-        <v>469200</v>
+        <v>87200</v>
       </c>
       <c r="H33" s="3">
-        <v>286000</v>
+        <v>466300</v>
       </c>
       <c r="I33" s="3">
-        <v>37000</v>
+        <v>284200</v>
       </c>
       <c r="J33" s="3">
+        <v>36800</v>
+      </c>
+      <c r="K33" s="3">
         <v>9600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-136600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-115200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-117000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-92000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>247800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>139800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>230400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-70100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-844500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>316800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>122100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-61600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>701700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-181000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-165400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>341600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>152100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>180300</v>
+        <v>595700</v>
       </c>
       <c r="E35" s="3">
-        <v>641600</v>
+        <v>179300</v>
       </c>
       <c r="F35" s="3">
-        <v>87700</v>
+        <v>637600</v>
       </c>
       <c r="G35" s="3">
-        <v>469200</v>
+        <v>87200</v>
       </c>
       <c r="H35" s="3">
-        <v>286000</v>
+        <v>466300</v>
       </c>
       <c r="I35" s="3">
-        <v>37000</v>
+        <v>284200</v>
       </c>
       <c r="J35" s="3">
+        <v>36800</v>
+      </c>
+      <c r="K35" s="3">
         <v>9600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-136600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-115200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-117000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-92000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>247800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>139800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>230400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-70100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-844500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>316800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>122100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-61600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>701700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-181000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-165400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>341600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>152100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,248 +3091,258 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6114500</v>
+        <v>6185800</v>
       </c>
       <c r="E41" s="3">
-        <v>5249500</v>
+        <v>5746400</v>
       </c>
       <c r="F41" s="3">
-        <v>5121900</v>
+        <v>5217100</v>
       </c>
       <c r="G41" s="3">
-        <v>4250700</v>
+        <v>5090200</v>
       </c>
       <c r="H41" s="3">
-        <v>2363300</v>
+        <v>4224400</v>
       </c>
       <c r="I41" s="3">
-        <v>2629700</v>
+        <v>2348700</v>
       </c>
       <c r="J41" s="3">
+        <v>2613400</v>
+      </c>
+      <c r="K41" s="3">
         <v>3191800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2880500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2736500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2828300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3937000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3210000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2519000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3680700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2784500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3800900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3143100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2822500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3514200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3454300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3275100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3121000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3162400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2475500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2617500</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2467300</v>
+        <v>3524000</v>
       </c>
       <c r="E42" s="3">
-        <v>3347000</v>
+        <v>2452100</v>
       </c>
       <c r="F42" s="3">
-        <v>2576300</v>
+        <v>3326300</v>
       </c>
       <c r="G42" s="3">
-        <v>2417000</v>
+        <v>2560400</v>
       </c>
       <c r="H42" s="3">
-        <v>3551300</v>
+        <v>2402000</v>
       </c>
       <c r="I42" s="3">
-        <v>3987600</v>
+        <v>3529300</v>
       </c>
       <c r="J42" s="3">
+        <v>3963000</v>
+      </c>
+      <c r="K42" s="3">
         <v>4270800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4193400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4082500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5081700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5015900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4270500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3454900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3245400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3519800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3955500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3637600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>4014100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>5033900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>5126900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>5590900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>5488700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>4760400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>4896000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>4036100</v>
       </c>
     </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1586200</v>
+        <v>1692600</v>
       </c>
       <c r="E43" s="3">
-        <v>1785700</v>
+        <v>1969100</v>
       </c>
       <c r="F43" s="3">
-        <v>1486000</v>
+        <v>1774700</v>
       </c>
       <c r="G43" s="3">
-        <v>1286900</v>
+        <v>1476800</v>
       </c>
       <c r="H43" s="3">
-        <v>1005700</v>
+        <v>1278900</v>
       </c>
       <c r="I43" s="3">
-        <v>855100</v>
+        <v>999400</v>
       </c>
       <c r="J43" s="3">
+        <v>849800</v>
+      </c>
+      <c r="K43" s="3">
         <v>757000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>549400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>871800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>718200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>758900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>605900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>824200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>844600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>755800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>804300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1647000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1431200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1577500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>929100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1112000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>987100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>898300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>742900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>735000</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3325,408 +3421,426 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2167500</v>
+        <v>2417200</v>
       </c>
       <c r="E45" s="3">
-        <v>2631200</v>
+        <v>2091700</v>
       </c>
       <c r="F45" s="3">
-        <v>2367200</v>
+        <v>2615000</v>
       </c>
       <c r="G45" s="3">
-        <v>2108500</v>
+        <v>2352600</v>
       </c>
       <c r="H45" s="3">
-        <v>1620400</v>
+        <v>2095500</v>
       </c>
       <c r="I45" s="3">
-        <v>1848100</v>
+        <v>1610400</v>
       </c>
       <c r="J45" s="3">
+        <v>1836700</v>
+      </c>
+      <c r="K45" s="3">
         <v>1498400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1280600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1437400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1925100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1475100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1362200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1277000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1835500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2296300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1638200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2292900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3369700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2122000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2560200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2099400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2669900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1838400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1400500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1190300</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12335500</v>
+        <v>13819700</v>
       </c>
       <c r="E46" s="3">
-        <v>13013500</v>
+        <v>12259200</v>
       </c>
       <c r="F46" s="3">
-        <v>11551400</v>
+        <v>12933000</v>
       </c>
       <c r="G46" s="3">
-        <v>10063100</v>
+        <v>11480000</v>
       </c>
       <c r="H46" s="3">
-        <v>8540700</v>
+        <v>10000800</v>
       </c>
       <c r="I46" s="3">
-        <v>9320600</v>
+        <v>8487900</v>
       </c>
       <c r="J46" s="3">
+        <v>9262900</v>
+      </c>
+      <c r="K46" s="3">
         <v>9717900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8903800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9128200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10553400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11186900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9448600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8075100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9606100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9356500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>10198900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10720600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11637500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12247600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12070600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12077400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12266700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10659600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9514900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8525300</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6859500</v>
+        <v>6586400</v>
       </c>
       <c r="E47" s="3">
-        <v>7432700</v>
+        <v>6820500</v>
       </c>
       <c r="F47" s="3">
-        <v>7612300</v>
+        <v>7386700</v>
       </c>
       <c r="G47" s="3">
-        <v>7885200</v>
+        <v>7565200</v>
       </c>
       <c r="H47" s="3">
-        <v>6979100</v>
+        <v>7836400</v>
       </c>
       <c r="I47" s="3">
-        <v>6534500</v>
+        <v>6935900</v>
       </c>
       <c r="J47" s="3">
+        <v>6494100</v>
+      </c>
+      <c r="K47" s="3">
         <v>6127300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5891600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6211700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5954300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6686600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6715800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6677100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7448000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7907200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8101400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8096900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7340700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>5350800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5212700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4122900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3724400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3907000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3652100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3737400</v>
       </c>
     </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>791700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>799000</v>
+      </c>
+      <c r="F48" s="3">
         <v>804000</v>
       </c>
-      <c r="E48" s="3">
-        <v>809000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>821200</v>
-      </c>
       <c r="G48" s="3">
-        <v>819800</v>
+        <v>816100</v>
       </c>
       <c r="H48" s="3">
-        <v>837300</v>
+        <v>814700</v>
       </c>
       <c r="I48" s="3">
-        <v>847300</v>
+        <v>832100</v>
       </c>
       <c r="J48" s="3">
+        <v>842100</v>
+      </c>
+      <c r="K48" s="3">
         <v>866400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>841700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>871400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>888100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>940900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>949500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>942000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>973700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>999100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1145700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1158300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1073400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1059800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1013900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>893200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>847700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>835300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>830000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>805800</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>10011700</v>
+        <v>9943800</v>
       </c>
       <c r="E49" s="3">
-        <v>10016900</v>
+        <v>9949700</v>
       </c>
       <c r="F49" s="3">
-        <v>10026100</v>
+        <v>9955000</v>
       </c>
       <c r="G49" s="3">
-        <v>10026300</v>
+        <v>9964100</v>
       </c>
       <c r="H49" s="3">
-        <v>10032000</v>
+        <v>9964200</v>
       </c>
       <c r="I49" s="3">
-        <v>10034700</v>
+        <v>9969900</v>
       </c>
       <c r="J49" s="3">
+        <v>9972700</v>
+      </c>
+      <c r="K49" s="3">
         <v>10044900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9989300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9996900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9984200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10310100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10103600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10119400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10649200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10705900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11274500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11291200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10976900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10908600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10878900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10928800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10452200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10276000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10086500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10056900</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,88 +4002,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>453800</v>
+        <v>428800</v>
       </c>
       <c r="E52" s="3">
-        <v>356600</v>
+        <v>447500</v>
       </c>
       <c r="F52" s="3">
-        <v>325300</v>
+        <v>354400</v>
       </c>
       <c r="G52" s="3">
-        <v>279300</v>
+        <v>323300</v>
       </c>
       <c r="H52" s="3">
-        <v>259800</v>
+        <v>277600</v>
       </c>
       <c r="I52" s="3">
-        <v>274100</v>
+        <v>258200</v>
       </c>
       <c r="J52" s="3">
+        <v>272500</v>
+      </c>
+      <c r="K52" s="3">
         <v>300700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>307500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>283800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>295000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>301200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>266400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>251400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>265900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>281600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>311100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>311700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>242200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>266800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>217700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>246100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>211200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>240300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>190500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>186800</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4168,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>30464400</v>
+        <v>31570400</v>
       </c>
       <c r="E54" s="3">
-        <v>31628700</v>
+        <v>30276000</v>
       </c>
       <c r="F54" s="3">
-        <v>30336400</v>
+        <v>31433100</v>
       </c>
       <c r="G54" s="3">
-        <v>29073700</v>
+        <v>30148700</v>
       </c>
       <c r="H54" s="3">
-        <v>26648900</v>
+        <v>28893800</v>
       </c>
       <c r="I54" s="3">
-        <v>27011300</v>
+        <v>26484000</v>
       </c>
       <c r="J54" s="3">
+        <v>26844200</v>
+      </c>
+      <c r="K54" s="3">
         <v>27057200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25933900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26491900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27675000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29425800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27483900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26065100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>28943000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>29250200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31031500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>31578700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>31270700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>29833700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>29393700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>28268500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>27502200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>25918200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>24274100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>23278200</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,488 +4315,507 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2288100</v>
+        <v>2450400</v>
       </c>
       <c r="E57" s="3">
-        <v>2526400</v>
+        <v>2274000</v>
       </c>
       <c r="F57" s="3">
-        <v>2047600</v>
+        <v>2510800</v>
       </c>
       <c r="G57" s="3">
-        <v>1569100</v>
+        <v>2035000</v>
       </c>
       <c r="H57" s="3">
-        <v>1052200</v>
+        <v>1559400</v>
       </c>
       <c r="I57" s="3">
-        <v>1027200</v>
+        <v>1045700</v>
       </c>
       <c r="J57" s="3">
+        <v>1020900</v>
+      </c>
+      <c r="K57" s="3">
         <v>937700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>580100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>831100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1009200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>934900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>692200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>627200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1038100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>659900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>777600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1939500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2061200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1974700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1668600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1781900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1975000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1593800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1351000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1070200</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3594600</v>
+        <v>5336700</v>
       </c>
       <c r="E58" s="3">
-        <v>4282800</v>
+        <v>3572400</v>
       </c>
       <c r="F58" s="3">
-        <v>4506200</v>
+        <v>4256300</v>
       </c>
       <c r="G58" s="3">
-        <v>5453900</v>
+        <v>4478300</v>
       </c>
       <c r="H58" s="3">
-        <v>4542300</v>
+        <v>5420200</v>
       </c>
       <c r="I58" s="3">
-        <v>4708300</v>
+        <v>4514200</v>
       </c>
       <c r="J58" s="3">
+        <v>4679200</v>
+      </c>
+      <c r="K58" s="3">
         <v>5032900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4262500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5504700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6219800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5823500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5678800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4686200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5012900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6203400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6370700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4814200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5658900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5758300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5769000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5478000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5232100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3509800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2952200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2341000</v>
       </c>
     </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4183800</v>
+        <v>4206100</v>
       </c>
       <c r="E59" s="3">
-        <v>4278800</v>
+        <v>4157900</v>
       </c>
       <c r="F59" s="3">
-        <v>3966800</v>
+        <v>4252300</v>
       </c>
       <c r="G59" s="3">
-        <v>3340500</v>
+        <v>3942300</v>
       </c>
       <c r="H59" s="3">
-        <v>2918900</v>
+        <v>3319800</v>
       </c>
       <c r="I59" s="3">
-        <v>2843100</v>
+        <v>2900800</v>
       </c>
       <c r="J59" s="3">
+        <v>2825500</v>
+      </c>
+      <c r="K59" s="3">
         <v>2745400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2588300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2807600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2900100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2988800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2765800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2811600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2909400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2944500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3547900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4160400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3692600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3668900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3135500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3203500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2823300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2821200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2478900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2698200</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10066600</v>
+        <v>11993300</v>
       </c>
       <c r="E60" s="3">
-        <v>11088000</v>
+        <v>10004300</v>
       </c>
       <c r="F60" s="3">
-        <v>10520600</v>
+        <v>11019400</v>
       </c>
       <c r="G60" s="3">
-        <v>10363500</v>
+        <v>10455500</v>
       </c>
       <c r="H60" s="3">
-        <v>8513400</v>
+        <v>10299400</v>
       </c>
       <c r="I60" s="3">
-        <v>8578600</v>
+        <v>8460800</v>
       </c>
       <c r="J60" s="3">
+        <v>8525600</v>
+      </c>
+      <c r="K60" s="3">
         <v>8716000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7430900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9143400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10129200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9747200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9136800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8125000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8960400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9807800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10696100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10914200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11412700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11401800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10573100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10463400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10030300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7924800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6782200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6049400</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2655100</v>
+        <v>1200300</v>
       </c>
       <c r="E61" s="3">
-        <v>2735500</v>
+        <v>2638700</v>
       </c>
       <c r="F61" s="3">
-        <v>2738300</v>
+        <v>2718600</v>
       </c>
       <c r="G61" s="3">
-        <v>1870200</v>
+        <v>2721300</v>
       </c>
       <c r="H61" s="3">
-        <v>1831900</v>
+        <v>1858700</v>
       </c>
       <c r="I61" s="3">
-        <v>2423800</v>
+        <v>1820500</v>
       </c>
       <c r="J61" s="3">
+        <v>2408800</v>
+      </c>
+      <c r="K61" s="3">
         <v>2419200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2803300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1531700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1690700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3228700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3251200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3162300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4710800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4136000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3674500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3082200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3172000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3311200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3721600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3673100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3785000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4291800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4171300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4192500</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>642400</v>
+        <v>608200</v>
       </c>
       <c r="E62" s="3">
-        <v>620700</v>
+        <v>638400</v>
       </c>
       <c r="F62" s="3">
-        <v>617400</v>
+        <v>616900</v>
       </c>
       <c r="G62" s="3">
-        <v>590300</v>
+        <v>613600</v>
       </c>
       <c r="H62" s="3">
-        <v>591700</v>
+        <v>586600</v>
       </c>
       <c r="I62" s="3">
-        <v>585600</v>
+        <v>588000</v>
       </c>
       <c r="J62" s="3">
+        <v>581900</v>
+      </c>
+      <c r="K62" s="3">
         <v>591100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>555800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>565000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>571400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>624300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>649400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>639600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>627800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>635000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>725400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>726500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>698100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>683800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>748700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>633900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>618100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>649800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>592000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>608800</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5060,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13478400</v>
+        <v>13917100</v>
       </c>
       <c r="E66" s="3">
-        <v>14554100</v>
+        <v>13395000</v>
       </c>
       <c r="F66" s="3">
-        <v>13980800</v>
+        <v>14464100</v>
       </c>
       <c r="G66" s="3">
-        <v>12926500</v>
+        <v>13894300</v>
       </c>
       <c r="H66" s="3">
-        <v>11039300</v>
+        <v>12846500</v>
       </c>
       <c r="I66" s="3">
-        <v>11687100</v>
+        <v>10971000</v>
       </c>
       <c r="J66" s="3">
+        <v>11614800</v>
+      </c>
+      <c r="K66" s="3">
         <v>11828700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10895200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11347700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12518600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13733100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13169000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12095800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14527600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14878300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15631500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15259700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15770800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15766100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15412600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15077400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14757400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13139500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>11814400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>11105900</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,16 +5506,19 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>16</v>
+      <c r="E72" s="3">
+        <v>4266100</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>16</v>
@@ -5352,11 +5526,11 @@
       <c r="G72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H72" s="3">
-        <v>2913900</v>
-      </c>
-      <c r="I72" s="3" t="s">
+      <c r="H72" s="3" t="s">
         <v>16</v>
+      </c>
+      <c r="I72" s="3">
+        <v>2895800</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>16</v>
@@ -5364,11 +5538,11 @@
       <c r="K72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M72" s="3">
         <v>2700400</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>16</v>
@@ -5376,11 +5550,11 @@
       <c r="O72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q72" s="3">
         <v>2798900</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>16</v>
@@ -5388,35 +5562,38 @@
       <c r="S72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U72" s="3">
         <v>3697600</v>
       </c>
-      <c r="U72" s="3" t="s">
+      <c r="V72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3152900</v>
       </c>
-      <c r="W72" s="3" t="s">
+      <c r="X72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2498900</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="Z72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB72" s="3">
         <v>2379000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2227000</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>16986000</v>
+        <v>17653300</v>
       </c>
       <c r="E76" s="3">
-        <v>17074600</v>
+        <v>16880900</v>
       </c>
       <c r="F76" s="3">
-        <v>16355600</v>
+        <v>16968900</v>
       </c>
       <c r="G76" s="3">
-        <v>16147200</v>
+        <v>16254400</v>
       </c>
       <c r="H76" s="3">
-        <v>15609600</v>
+        <v>16047300</v>
       </c>
       <c r="I76" s="3">
-        <v>15324200</v>
+        <v>15513000</v>
       </c>
       <c r="J76" s="3">
+        <v>15229400</v>
+      </c>
+      <c r="K76" s="3">
         <v>15228500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15038700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15144200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15156500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15692600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14314900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13969300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14415400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14371900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15400100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16319000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15499900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14067500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13981000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13191100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12744800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12778800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12459700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12172300</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>180300</v>
+        <v>595700</v>
       </c>
       <c r="E81" s="3">
-        <v>641600</v>
+        <v>179300</v>
       </c>
       <c r="F81" s="3">
-        <v>87700</v>
+        <v>637600</v>
       </c>
       <c r="G81" s="3">
-        <v>469200</v>
+        <v>87200</v>
       </c>
       <c r="H81" s="3">
-        <v>286000</v>
+        <v>466300</v>
       </c>
       <c r="I81" s="3">
-        <v>37000</v>
+        <v>284200</v>
       </c>
       <c r="J81" s="3">
+        <v>36800</v>
+      </c>
+      <c r="K81" s="3">
         <v>9600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-136600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-115200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-117000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-92000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>247800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>139800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>230400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-70100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-844500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>316800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>122100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-61600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>701700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-181000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-165400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>341600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>152100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6208,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6060,15 +6259,15 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>172900</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,8 +6704,11 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6540,15 +6757,15 @@
       <c r="R89" s="3">
         <v>0</v>
       </c>
-      <c r="S89" s="3" t="s">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1156900</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
         <v>0</v>
       </c>
@@ -6570,8 +6787,11 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,8 +6820,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6650,15 +6871,15 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-129800</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -6680,8 +6901,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,8 +7067,11 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6890,15 +7120,15 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-380700</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
@@ -6920,8 +7150,11 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,8 +7513,11 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7320,15 +7566,15 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-      <c r="S100" s="3" t="s">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1460200</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
@@ -7350,8 +7596,11 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7400,15 +7649,15 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3" t="s">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>48700</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
@@ -7430,8 +7679,11 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7480,15 +7732,15 @@
       <c r="R102" s="3">
         <v>0</v>
       </c>
-      <c r="S102" s="3" t="s">
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-635300</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
         <v>0</v>
       </c>
@@ -7508,6 +7760,9 @@
         <v>0</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TCOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TCOM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>TCOM</t>
   </si>
@@ -656,378 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1644800</v>
+        <v>1800600</v>
       </c>
       <c r="E8" s="3">
-        <v>1426500</v>
+        <v>1678400</v>
       </c>
       <c r="F8" s="3">
-        <v>1898300</v>
+        <v>1455600</v>
       </c>
       <c r="G8" s="3">
-        <v>1553900</v>
+        <v>1937100</v>
       </c>
       <c r="H8" s="3">
-        <v>1270800</v>
+        <v>1585600</v>
       </c>
       <c r="I8" s="3">
-        <v>694500</v>
+        <v>1296700</v>
       </c>
       <c r="J8" s="3">
+        <v>708700</v>
+      </c>
+      <c r="K8" s="3">
         <v>952200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>557600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>567400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>646400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>736300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>837300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>571800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>691000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>797600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>465500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>746400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1314900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1613100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1327800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1241900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1150000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1358600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1050100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>965800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>885700</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>309200</v>
+        <v>325900</v>
       </c>
       <c r="E9" s="3">
-        <v>277700</v>
+        <v>315500</v>
       </c>
       <c r="F9" s="3">
-        <v>340800</v>
+        <v>283400</v>
       </c>
       <c r="G9" s="3">
-        <v>277300</v>
+        <v>347800</v>
       </c>
       <c r="H9" s="3">
-        <v>226200</v>
+        <v>282900</v>
       </c>
       <c r="I9" s="3">
-        <v>165700</v>
+        <v>230800</v>
       </c>
       <c r="J9" s="3">
+        <v>169000</v>
+      </c>
+      <c r="K9" s="3">
         <v>175600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>135700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>147300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>154400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>168500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>173800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>143900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>126700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>150300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>128500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>192500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>272600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>332100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>274700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>256900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>246400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>289200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>210800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>178500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>152200</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1335600</v>
+        <v>1474700</v>
       </c>
       <c r="E10" s="3">
-        <v>1148800</v>
+        <v>1362900</v>
       </c>
       <c r="F10" s="3">
-        <v>1557500</v>
+        <v>1172200</v>
       </c>
       <c r="G10" s="3">
-        <v>1276600</v>
+        <v>1589300</v>
       </c>
       <c r="H10" s="3">
-        <v>1044600</v>
+        <v>1302700</v>
       </c>
       <c r="I10" s="3">
-        <v>528900</v>
+        <v>1065900</v>
       </c>
       <c r="J10" s="3">
+        <v>539700</v>
+      </c>
+      <c r="K10" s="3">
         <v>776600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>421900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>420000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>492000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>567800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>663400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>427900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>564300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>647400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>337000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>553900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1042300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1281000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1053100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>985000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>903600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1069500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>839400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>787300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>733500</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,91 +1070,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>429500</v>
+        <v>422000</v>
       </c>
       <c r="E12" s="3">
-        <v>402900</v>
+        <v>438300</v>
       </c>
       <c r="F12" s="3">
-        <v>494200</v>
+        <v>411100</v>
       </c>
       <c r="G12" s="3">
-        <v>408000</v>
+        <v>504300</v>
       </c>
       <c r="H12" s="3">
-        <v>369400</v>
+        <v>416300</v>
       </c>
       <c r="I12" s="3">
-        <v>290700</v>
+        <v>377000</v>
       </c>
       <c r="J12" s="3">
+        <v>296600</v>
+      </c>
+      <c r="K12" s="3">
         <v>344200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>246300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>272600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>308700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>317600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>316400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>309700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>301000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>293200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>265400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>267600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>425000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>429600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>403600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>387000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>413500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>361800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>323000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>309900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>297600</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1306,8 +1326,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1186800</v>
+        <v>1299400</v>
       </c>
       <c r="E17" s="3">
-        <v>1123000</v>
+        <v>1211000</v>
       </c>
       <c r="F17" s="3">
-        <v>1358300</v>
+        <v>1145900</v>
       </c>
       <c r="G17" s="3">
-        <v>1142600</v>
+        <v>1386000</v>
       </c>
       <c r="H17" s="3">
-        <v>961200</v>
+        <v>1165900</v>
       </c>
       <c r="I17" s="3">
-        <v>727700</v>
+        <v>980800</v>
       </c>
       <c r="J17" s="3">
+        <v>742500</v>
+      </c>
+      <c r="K17" s="3">
         <v>834200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>580800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>616900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>743600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>770200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>790900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>681400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>693200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>682300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>566900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>984400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1223400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1267900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1124200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1107300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1178800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1143700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>946300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>881100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>842200</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>458000</v>
+        <v>501200</v>
       </c>
       <c r="E18" s="3">
-        <v>303500</v>
+        <v>467300</v>
       </c>
       <c r="F18" s="3">
-        <v>540100</v>
+        <v>309700</v>
       </c>
       <c r="G18" s="3">
-        <v>411300</v>
+        <v>551100</v>
       </c>
       <c r="H18" s="3">
-        <v>309600</v>
+        <v>419700</v>
       </c>
       <c r="I18" s="3">
-        <v>-33200</v>
+        <v>315900</v>
       </c>
       <c r="J18" s="3">
+        <v>-33800</v>
+      </c>
+      <c r="K18" s="3">
         <v>118000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-23200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-49600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-97200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-33900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>46300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-109600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>115400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-101400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-238100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>91500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>345200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>203700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>134600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-28800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>214900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>103900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>84700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>43500</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1614,91 +1647,95 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>186700</v>
+        <v>63600</v>
       </c>
       <c r="E20" s="3">
-        <v>-42800</v>
+        <v>190500</v>
       </c>
       <c r="F20" s="3">
-        <v>150300</v>
+        <v>-43700</v>
       </c>
       <c r="G20" s="3">
-        <v>-200100</v>
+        <v>153400</v>
       </c>
       <c r="H20" s="3">
-        <v>289200</v>
+        <v>-204100</v>
       </c>
       <c r="I20" s="3">
-        <v>429100</v>
+        <v>295100</v>
       </c>
       <c r="J20" s="3">
+        <v>437900</v>
+      </c>
+      <c r="K20" s="3">
         <v>8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>140800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-16000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>14200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-53400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>407300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>166800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>242600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>349100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-522800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>364600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-129300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-129900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>776300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-80500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-305600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>370200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>125800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>96600</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1753,11 +1790,11 @@
       <c r="T21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V21" s="3">
         <v>629000</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>16</v>
@@ -1780,257 +1817,269 @@
       <c r="AC21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>68900</v>
+        <v>72500</v>
       </c>
       <c r="E22" s="3">
-        <v>68700</v>
+        <v>70300</v>
       </c>
       <c r="F22" s="3">
-        <v>73100</v>
+        <v>70100</v>
       </c>
       <c r="G22" s="3">
-        <v>76700</v>
+        <v>74600</v>
       </c>
       <c r="H22" s="3">
-        <v>67100</v>
+        <v>78200</v>
       </c>
       <c r="I22" s="3">
-        <v>45600</v>
+        <v>68500</v>
       </c>
       <c r="J22" s="3">
+        <v>46500</v>
+      </c>
+      <c r="K22" s="3">
         <v>68000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>48800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>47100</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="N22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>117700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>59400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>56700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>52500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>62800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>67900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>70700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>61100</v>
-      </c>
-      <c r="V22" s="3">
-        <v>65100</v>
       </c>
       <c r="W22" s="3">
         <v>65100</v>
       </c>
       <c r="X22" s="3">
+        <v>65100</v>
+      </c>
+      <c r="Y22" s="3">
         <v>67100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>64200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>57100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>53200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>46200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>575700</v>
+        <v>492300</v>
       </c>
       <c r="E23" s="3">
-        <v>192000</v>
+        <v>587500</v>
       </c>
       <c r="F23" s="3">
-        <v>617300</v>
+        <v>196000</v>
       </c>
       <c r="G23" s="3">
-        <v>134600</v>
+        <v>629900</v>
       </c>
       <c r="H23" s="3">
-        <v>531600</v>
+        <v>137300</v>
       </c>
       <c r="I23" s="3">
-        <v>350400</v>
+        <v>542500</v>
       </c>
       <c r="J23" s="3">
+        <v>357500</v>
+      </c>
+      <c r="K23" s="3">
         <v>58000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>68800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-112700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-101900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-137400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-66500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>241100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>112100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>295100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>179800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-831600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>395000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>150700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>843800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-173400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-147700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>420800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>164300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>93500</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>91700</v>
+        <v>97700</v>
       </c>
       <c r="E24" s="3">
-        <v>55100</v>
+        <v>93600</v>
       </c>
       <c r="F24" s="3">
-        <v>61900</v>
+        <v>56300</v>
       </c>
       <c r="G24" s="3">
-        <v>77600</v>
+        <v>63200</v>
       </c>
       <c r="H24" s="3">
-        <v>47100</v>
+        <v>79200</v>
       </c>
       <c r="I24" s="3">
-        <v>34000</v>
+        <v>48100</v>
       </c>
       <c r="J24" s="3">
+        <v>34700</v>
+      </c>
+      <c r="K24" s="3">
         <v>38300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>24100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>13100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>13800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>22700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>35800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>29600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-40100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>57400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>56200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>51300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>103000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>37300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>46200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>25700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>484000</v>
+        <v>394600</v>
       </c>
       <c r="E26" s="3">
-        <v>136900</v>
+        <v>493900</v>
       </c>
       <c r="F26" s="3">
-        <v>555400</v>
+        <v>139700</v>
       </c>
       <c r="G26" s="3">
-        <v>56900</v>
+        <v>566700</v>
       </c>
       <c r="H26" s="3">
-        <v>484500</v>
+        <v>58100</v>
       </c>
       <c r="I26" s="3">
-        <v>316400</v>
+        <v>494400</v>
       </c>
       <c r="J26" s="3">
+        <v>322800</v>
+      </c>
+      <c r="K26" s="3">
         <v>19800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>44800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-110700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-107000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-150500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-80300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>235400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>89400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>259300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>150200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-791500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>337600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>94500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-42600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>740800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-178700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-185000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>374600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>138600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>595700</v>
+        <v>540400</v>
       </c>
       <c r="E27" s="3">
-        <v>179300</v>
+        <v>607900</v>
       </c>
       <c r="F27" s="3">
-        <v>637600</v>
+        <v>183000</v>
       </c>
       <c r="G27" s="3">
-        <v>87200</v>
+        <v>650600</v>
       </c>
       <c r="H27" s="3">
-        <v>466300</v>
+        <v>89000</v>
       </c>
       <c r="I27" s="3">
-        <v>284200</v>
+        <v>475800</v>
       </c>
       <c r="J27" s="3">
+        <v>290000</v>
+      </c>
+      <c r="K27" s="3">
         <v>36800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-136600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-115200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-117000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-92000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>247800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>139800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>230400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-70100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-844500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>316800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>122100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-61600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>701700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-181000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-165400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>341600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>152100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,174 +2677,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-186700</v>
+        <v>-63600</v>
       </c>
       <c r="E32" s="3">
-        <v>42800</v>
+        <v>-190500</v>
       </c>
       <c r="F32" s="3">
-        <v>-150300</v>
+        <v>43700</v>
       </c>
       <c r="G32" s="3">
-        <v>200100</v>
+        <v>-153400</v>
       </c>
       <c r="H32" s="3">
-        <v>-289200</v>
+        <v>204100</v>
       </c>
       <c r="I32" s="3">
-        <v>-429100</v>
+        <v>-295100</v>
       </c>
       <c r="J32" s="3">
+        <v>-437900</v>
+      </c>
+      <c r="K32" s="3">
         <v>-8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-140800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>16000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-14200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>53400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-407300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-166800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-242600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-349100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>522800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-364600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>129300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>129900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-776300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>80500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>305600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-370200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-125800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-96600</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>595700</v>
+        <v>540400</v>
       </c>
       <c r="E33" s="3">
-        <v>179300</v>
+        <v>607900</v>
       </c>
       <c r="F33" s="3">
-        <v>637600</v>
+        <v>183000</v>
       </c>
       <c r="G33" s="3">
-        <v>87200</v>
+        <v>650600</v>
       </c>
       <c r="H33" s="3">
-        <v>466300</v>
+        <v>89000</v>
       </c>
       <c r="I33" s="3">
-        <v>284200</v>
+        <v>475800</v>
       </c>
       <c r="J33" s="3">
+        <v>290000</v>
+      </c>
+      <c r="K33" s="3">
         <v>36800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-136600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-115200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-117000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-92000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>247800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>139800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>230400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-70100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-844500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>316800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>122100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-61600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>701700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-181000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-165400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>341600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>152100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>595700</v>
+        <v>540400</v>
       </c>
       <c r="E35" s="3">
-        <v>179300</v>
+        <v>607900</v>
       </c>
       <c r="F35" s="3">
-        <v>637600</v>
+        <v>183000</v>
       </c>
       <c r="G35" s="3">
-        <v>87200</v>
+        <v>650600</v>
       </c>
       <c r="H35" s="3">
-        <v>466300</v>
+        <v>89000</v>
       </c>
       <c r="I35" s="3">
-        <v>284200</v>
+        <v>475800</v>
       </c>
       <c r="J35" s="3">
+        <v>290000</v>
+      </c>
+      <c r="K35" s="3">
         <v>36800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-136600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-115200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-117000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-92000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>247800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>139800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>230400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-70100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-844500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>316800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>122100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-61600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>701700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-181000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-165400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>341600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>152100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,257 +3178,267 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6185800</v>
+        <v>7267900</v>
       </c>
       <c r="E41" s="3">
-        <v>5746400</v>
+        <v>6312100</v>
       </c>
       <c r="F41" s="3">
-        <v>5217100</v>
+        <v>5863600</v>
       </c>
       <c r="G41" s="3">
-        <v>5090200</v>
+        <v>5323500</v>
       </c>
       <c r="H41" s="3">
-        <v>4224400</v>
+        <v>5194100</v>
       </c>
       <c r="I41" s="3">
-        <v>2348700</v>
+        <v>4310600</v>
       </c>
       <c r="J41" s="3">
+        <v>2396700</v>
+      </c>
+      <c r="K41" s="3">
         <v>2613400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3191800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2880500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2736500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2828300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3937000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3210000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2519000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3680700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2784500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3800900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3143100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2822500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3514200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3454300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3275100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3121000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3162400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2475500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2617500</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3524000</v>
+        <v>5387700</v>
       </c>
       <c r="E42" s="3">
-        <v>2452100</v>
+        <v>3596000</v>
       </c>
       <c r="F42" s="3">
-        <v>3326300</v>
+        <v>2502100</v>
       </c>
       <c r="G42" s="3">
-        <v>2560400</v>
+        <v>3394200</v>
       </c>
       <c r="H42" s="3">
-        <v>2402000</v>
+        <v>2612600</v>
       </c>
       <c r="I42" s="3">
-        <v>3529300</v>
+        <v>2451100</v>
       </c>
       <c r="J42" s="3">
+        <v>3601300</v>
+      </c>
+      <c r="K42" s="3">
         <v>3963000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4270800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4193400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4082500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5081700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5015900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4270500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3454900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3245400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3519800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3955500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3637600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>4014100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>5033900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>5126900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>5590900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>5488700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>4760400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>4896000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>4036100</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1692600</v>
+        <v>1819600</v>
       </c>
       <c r="E43" s="3">
-        <v>1969100</v>
+        <v>1727100</v>
       </c>
       <c r="F43" s="3">
-        <v>1774700</v>
+        <v>2009200</v>
       </c>
       <c r="G43" s="3">
-        <v>1476800</v>
+        <v>1810900</v>
       </c>
       <c r="H43" s="3">
-        <v>1278900</v>
+        <v>1506900</v>
       </c>
       <c r="I43" s="3">
-        <v>999400</v>
+        <v>1305100</v>
       </c>
       <c r="J43" s="3">
+        <v>1019800</v>
+      </c>
+      <c r="K43" s="3">
         <v>849800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>757000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>549400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>871800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>718200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>758900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>605900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>824200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>844600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>755800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>804300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1647000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1431200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1577500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>929100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1112000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>987100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>898300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>742900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>735000</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3424,423 +3520,441 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2417200</v>
+        <v>2659300</v>
       </c>
       <c r="E45" s="3">
-        <v>2091700</v>
+        <v>2466600</v>
       </c>
       <c r="F45" s="3">
-        <v>2615000</v>
+        <v>2134400</v>
       </c>
       <c r="G45" s="3">
-        <v>2352600</v>
+        <v>2668300</v>
       </c>
       <c r="H45" s="3">
-        <v>2095500</v>
+        <v>2400600</v>
       </c>
       <c r="I45" s="3">
-        <v>1610400</v>
+        <v>2138200</v>
       </c>
       <c r="J45" s="3">
+        <v>1643300</v>
+      </c>
+      <c r="K45" s="3">
         <v>1836700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1498400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1280600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1437400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1925100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1475100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1362200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1277000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1835500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2296300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1638200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2292900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3369700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2122000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2560200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2099400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2669900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1838400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1400500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1190300</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>13819700</v>
+        <v>17134600</v>
       </c>
       <c r="E46" s="3">
-        <v>12259200</v>
+        <v>14101800</v>
       </c>
       <c r="F46" s="3">
-        <v>12933000</v>
+        <v>12509400</v>
       </c>
       <c r="G46" s="3">
-        <v>11480000</v>
+        <v>13197000</v>
       </c>
       <c r="H46" s="3">
-        <v>10000800</v>
+        <v>11714300</v>
       </c>
       <c r="I46" s="3">
-        <v>8487900</v>
+        <v>10205000</v>
       </c>
       <c r="J46" s="3">
+        <v>8661100</v>
+      </c>
+      <c r="K46" s="3">
         <v>9262900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9717900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8903800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9128200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10553400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11186900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9448600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8075100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9606100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9356500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10198900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10720600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11637500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12247600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12070600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12077400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12266700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10659600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9514900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8525300</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6586400</v>
+        <v>6399400</v>
       </c>
       <c r="E47" s="3">
-        <v>6820500</v>
+        <v>6720800</v>
       </c>
       <c r="F47" s="3">
-        <v>7386700</v>
+        <v>6959800</v>
       </c>
       <c r="G47" s="3">
-        <v>7565200</v>
+        <v>7537500</v>
       </c>
       <c r="H47" s="3">
-        <v>7836400</v>
+        <v>7719600</v>
       </c>
       <c r="I47" s="3">
-        <v>6935900</v>
+        <v>7996400</v>
       </c>
       <c r="J47" s="3">
+        <v>7077500</v>
+      </c>
+      <c r="K47" s="3">
         <v>6494100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6127300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5891600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6211700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5954300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6686600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6715800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6677100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7448000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7907200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8101400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8096900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7340700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5350800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5212700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4122900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3724400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3907000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3652100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3737400</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>791700</v>
+        <v>821100</v>
       </c>
       <c r="E48" s="3">
-        <v>799000</v>
+        <v>807800</v>
       </c>
       <c r="F48" s="3">
-        <v>804000</v>
+        <v>815300</v>
       </c>
       <c r="G48" s="3">
-        <v>816100</v>
+        <v>820400</v>
       </c>
       <c r="H48" s="3">
-        <v>814700</v>
+        <v>832800</v>
       </c>
       <c r="I48" s="3">
-        <v>832100</v>
+        <v>831400</v>
       </c>
       <c r="J48" s="3">
+        <v>849100</v>
+      </c>
+      <c r="K48" s="3">
         <v>842100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>866400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>841700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>871400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>888100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>940900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>949500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>942000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>973700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>999100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1145700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1158300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1073400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1059800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1013900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>893200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>847700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>835300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>830000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>805800</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9943800</v>
+        <v>10141000</v>
       </c>
       <c r="E49" s="3">
-        <v>9949700</v>
+        <v>10146800</v>
       </c>
       <c r="F49" s="3">
-        <v>9955000</v>
+        <v>10152800</v>
       </c>
       <c r="G49" s="3">
-        <v>9964100</v>
+        <v>10158200</v>
       </c>
       <c r="H49" s="3">
-        <v>9964200</v>
+        <v>10167500</v>
       </c>
       <c r="I49" s="3">
-        <v>9969900</v>
+        <v>10167600</v>
       </c>
       <c r="J49" s="3">
+        <v>10173400</v>
+      </c>
+      <c r="K49" s="3">
         <v>9972700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10044900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9989300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9996900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9984200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10310100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10103600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10119400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10649200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10705900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11274500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>11291200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10976900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10908600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10878900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10928800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10452200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10276000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10086500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>10056900</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,91 +4122,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>428800</v>
+        <v>442100</v>
       </c>
       <c r="E52" s="3">
-        <v>447500</v>
+        <v>437600</v>
       </c>
       <c r="F52" s="3">
-        <v>354400</v>
+        <v>456600</v>
       </c>
       <c r="G52" s="3">
-        <v>323300</v>
+        <v>361600</v>
       </c>
       <c r="H52" s="3">
-        <v>277600</v>
+        <v>329900</v>
       </c>
       <c r="I52" s="3">
-        <v>258200</v>
+        <v>283200</v>
       </c>
       <c r="J52" s="3">
+        <v>263500</v>
+      </c>
+      <c r="K52" s="3">
         <v>272500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>300700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>307500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>283800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>295000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>301200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>266400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>251400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>265900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>281600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>311100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>311700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>242200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>266800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>217700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>246100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>211200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>240300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>190500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>186800</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>31570400</v>
+        <v>34938100</v>
       </c>
       <c r="E54" s="3">
-        <v>30276000</v>
+        <v>32214800</v>
       </c>
       <c r="F54" s="3">
-        <v>31433100</v>
+        <v>30893900</v>
       </c>
       <c r="G54" s="3">
-        <v>30148700</v>
+        <v>32074600</v>
       </c>
       <c r="H54" s="3">
-        <v>28893800</v>
+        <v>30764100</v>
       </c>
       <c r="I54" s="3">
-        <v>26484000</v>
+        <v>29483600</v>
       </c>
       <c r="J54" s="3">
+        <v>27024600</v>
+      </c>
+      <c r="K54" s="3">
         <v>26844200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27057200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25933900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26491900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27675000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29425800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>27483900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26065100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>28943000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>29250200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>31031500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>31578700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>31270700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>29833700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>29393700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>28268500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>27502200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>25918200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>24274100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>23278200</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,506 +4446,525 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2450400</v>
+        <v>2705300</v>
       </c>
       <c r="E57" s="3">
-        <v>2274000</v>
+        <v>2500400</v>
       </c>
       <c r="F57" s="3">
-        <v>2510800</v>
+        <v>2320400</v>
       </c>
       <c r="G57" s="3">
-        <v>2035000</v>
+        <v>2562000</v>
       </c>
       <c r="H57" s="3">
-        <v>1559400</v>
+        <v>2076500</v>
       </c>
       <c r="I57" s="3">
-        <v>1045700</v>
+        <v>1591200</v>
       </c>
       <c r="J57" s="3">
+        <v>1067100</v>
+      </c>
+      <c r="K57" s="3">
         <v>1020900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>937700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>580100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>831100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1009200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>934900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>692200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>627200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1038100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>659900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>777600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1939500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2061200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1974700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1668600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1781900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1975000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1593800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1351000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1070200</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5336700</v>
+        <v>5572900</v>
       </c>
       <c r="E58" s="3">
-        <v>3572400</v>
+        <v>5445600</v>
       </c>
       <c r="F58" s="3">
-        <v>4256300</v>
+        <v>3645300</v>
       </c>
       <c r="G58" s="3">
-        <v>4478300</v>
+        <v>4343200</v>
       </c>
       <c r="H58" s="3">
-        <v>5420200</v>
+        <v>4569700</v>
       </c>
       <c r="I58" s="3">
-        <v>4514200</v>
+        <v>5530800</v>
       </c>
       <c r="J58" s="3">
+        <v>4606400</v>
+      </c>
+      <c r="K58" s="3">
         <v>4679200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5032900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4262500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5504700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6219800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5823500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5678800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4686200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5012900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6203400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6370700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4814200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5658900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5758300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5769000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5478000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5232100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3509800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2952200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2341000</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4206100</v>
+        <v>4708300</v>
       </c>
       <c r="E59" s="3">
-        <v>4157900</v>
+        <v>4292000</v>
       </c>
       <c r="F59" s="3">
-        <v>4252300</v>
+        <v>4242800</v>
       </c>
       <c r="G59" s="3">
-        <v>3942300</v>
+        <v>4339100</v>
       </c>
       <c r="H59" s="3">
-        <v>3319800</v>
+        <v>4022700</v>
       </c>
       <c r="I59" s="3">
-        <v>2900800</v>
+        <v>3387600</v>
       </c>
       <c r="J59" s="3">
+        <v>2960000</v>
+      </c>
+      <c r="K59" s="3">
         <v>2825500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2745400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2588300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2807600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2900100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2988800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2765800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2811600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2909400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2944500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3547900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4160400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3692600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3668900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3135500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3203500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2823300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2821200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2478900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2698200</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>11993300</v>
+        <v>12986500</v>
       </c>
       <c r="E60" s="3">
-        <v>10004300</v>
+        <v>12238100</v>
       </c>
       <c r="F60" s="3">
-        <v>11019400</v>
+        <v>10208500</v>
       </c>
       <c r="G60" s="3">
-        <v>10455500</v>
+        <v>11244300</v>
       </c>
       <c r="H60" s="3">
-        <v>10299400</v>
+        <v>10668900</v>
       </c>
       <c r="I60" s="3">
-        <v>8460800</v>
+        <v>10509600</v>
       </c>
       <c r="J60" s="3">
+        <v>8633500</v>
+      </c>
+      <c r="K60" s="3">
         <v>8525600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8716000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7430900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9143400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10129200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9747200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9136800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8125000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8960400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9807800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10696100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10914200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11412700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11401800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10573100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10463400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10030300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7924800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6782200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6049400</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1200300</v>
+        <v>2824400</v>
       </c>
       <c r="E61" s="3">
-        <v>2638700</v>
+        <v>1224800</v>
       </c>
       <c r="F61" s="3">
-        <v>2718600</v>
+        <v>2692600</v>
       </c>
       <c r="G61" s="3">
-        <v>2721300</v>
+        <v>2774100</v>
       </c>
       <c r="H61" s="3">
-        <v>1858700</v>
+        <v>2776900</v>
       </c>
       <c r="I61" s="3">
-        <v>1820500</v>
+        <v>1896600</v>
       </c>
       <c r="J61" s="3">
+        <v>1857700</v>
+      </c>
+      <c r="K61" s="3">
         <v>2408800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2419200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2803300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1531700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1690700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3228700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3251200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3162300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4710800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4136000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3674500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3082200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3172000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3311200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3721600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3673100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3785000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4291800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4171300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4192500</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>608200</v>
+        <v>603500</v>
       </c>
       <c r="E62" s="3">
-        <v>638400</v>
+        <v>620600</v>
       </c>
       <c r="F62" s="3">
-        <v>616900</v>
+        <v>651500</v>
       </c>
       <c r="G62" s="3">
-        <v>613600</v>
+        <v>629500</v>
       </c>
       <c r="H62" s="3">
-        <v>586600</v>
+        <v>626100</v>
       </c>
       <c r="I62" s="3">
-        <v>588000</v>
+        <v>598600</v>
       </c>
       <c r="J62" s="3">
+        <v>600000</v>
+      </c>
+      <c r="K62" s="3">
         <v>581900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>591100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>555800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>565000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>571400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>624300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>649400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>639600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>627800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>635000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>725400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>726500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>698100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>683800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>748700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>633900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>618100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>649800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>592000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>608800</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5218,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13917100</v>
+        <v>16540200</v>
       </c>
       <c r="E66" s="3">
-        <v>13395000</v>
+        <v>14201200</v>
       </c>
       <c r="F66" s="3">
-        <v>14464100</v>
+        <v>13668400</v>
       </c>
       <c r="G66" s="3">
-        <v>13894300</v>
+        <v>14759300</v>
       </c>
       <c r="H66" s="3">
-        <v>12846500</v>
+        <v>14177900</v>
       </c>
       <c r="I66" s="3">
-        <v>10971000</v>
+        <v>13108700</v>
       </c>
       <c r="J66" s="3">
+        <v>11194900</v>
+      </c>
+      <c r="K66" s="3">
         <v>11614800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11828700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10895200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11347700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12518600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13733100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13169000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12095800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14527600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14878300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15631500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15259700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15770800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15766100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15412600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15077400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14757400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13139500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>11814400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>11105900</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,19 +5680,22 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E72" s="3">
-        <v>4266100</v>
-      </c>
-      <c r="F72" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>16</v>
+      </c>
+      <c r="F72" s="3">
+        <v>4353200</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>16</v>
@@ -5529,11 +5703,11 @@
       <c r="H72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I72" s="3">
-        <v>2895800</v>
-      </c>
-      <c r="J72" s="3" t="s">
+      <c r="I72" s="3" t="s">
         <v>16</v>
+      </c>
+      <c r="J72" s="3">
+        <v>2954900</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>16</v>
@@ -5541,11 +5715,11 @@
       <c r="L72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N72" s="3">
         <v>2700400</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>16</v>
@@ -5553,11 +5727,11 @@
       <c r="P72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R72" s="3">
         <v>2798900</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>16</v>
@@ -5565,35 +5739,38 @@
       <c r="T72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V72" s="3">
         <v>3697600</v>
       </c>
-      <c r="V72" s="3" t="s">
+      <c r="W72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3152900</v>
       </c>
-      <c r="X72" s="3" t="s">
+      <c r="Y72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2498900</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC72" s="3">
         <v>2379000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2227000</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>17653300</v>
+        <v>18397900</v>
       </c>
       <c r="E76" s="3">
-        <v>16880900</v>
+        <v>18013600</v>
       </c>
       <c r="F76" s="3">
-        <v>16968900</v>
+        <v>17225500</v>
       </c>
       <c r="G76" s="3">
-        <v>16254400</v>
+        <v>17315300</v>
       </c>
       <c r="H76" s="3">
-        <v>16047300</v>
+        <v>16586200</v>
       </c>
       <c r="I76" s="3">
-        <v>15513000</v>
+        <v>16374800</v>
       </c>
       <c r="J76" s="3">
+        <v>15829700</v>
+      </c>
+      <c r="K76" s="3">
         <v>15229400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15228500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15038700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15144200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15156500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15692600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14314900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13969300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14415400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14371900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15400100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16319000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15499900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14067500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13981000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13191100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12744800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12778800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12459700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12172300</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>595700</v>
+        <v>540400</v>
       </c>
       <c r="E81" s="3">
-        <v>179300</v>
+        <v>607900</v>
       </c>
       <c r="F81" s="3">
-        <v>637600</v>
+        <v>183000</v>
       </c>
       <c r="G81" s="3">
-        <v>87200</v>
+        <v>650600</v>
       </c>
       <c r="H81" s="3">
-        <v>466300</v>
+        <v>89000</v>
       </c>
       <c r="I81" s="3">
-        <v>284200</v>
+        <v>475800</v>
       </c>
       <c r="J81" s="3">
+        <v>290000</v>
+      </c>
+      <c r="K81" s="3">
         <v>36800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-136600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-115200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-117000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-92000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>247800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>139800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>230400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-70100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-844500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>316800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>122100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-61600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>701700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-181000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-165400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>341600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>152100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6262,15 +6461,15 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>172900</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,8 +6921,11 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6760,15 +6977,15 @@
       <c r="S89" s="3">
         <v>0</v>
       </c>
-      <c r="T89" s="3" t="s">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1156900</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
         <v>0</v>
       </c>
@@ -6790,8 +7007,11 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7041,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6874,15 +7095,15 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-129800</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,8 +7297,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7123,15 +7353,15 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-380700</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
@@ -7153,8 +7383,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,8 +7759,11 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7569,15 +7815,15 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-      <c r="T100" s="3" t="s">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1460200</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -7599,8 +7845,11 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7652,15 +7901,15 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>48700</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
@@ -7682,8 +7931,11 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7735,15 +7987,15 @@
       <c r="S102" s="3">
         <v>0</v>
       </c>
-      <c r="T102" s="3" t="s">
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-635300</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
       <c r="W102" s="3">
         <v>0</v>
       </c>
@@ -7763,6 +8015,9 @@
         <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TCOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TCOM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
   <si>
     <t>TCOM</t>
   </si>
@@ -656,391 +656,404 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1800600</v>
+        <v>2262900</v>
       </c>
       <c r="E8" s="3">
-        <v>1678400</v>
+        <v>1757600</v>
       </c>
       <c r="F8" s="3">
-        <v>1455600</v>
+        <v>1648800</v>
       </c>
       <c r="G8" s="3">
-        <v>1937100</v>
+        <v>1456100</v>
       </c>
       <c r="H8" s="3">
-        <v>1585600</v>
+        <v>1883100</v>
       </c>
       <c r="I8" s="3">
-        <v>1296700</v>
+        <v>1550800</v>
       </c>
       <c r="J8" s="3">
+        <v>1339000</v>
+      </c>
+      <c r="K8" s="3">
         <v>708700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>952200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>557600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>567400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>646400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>736300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>837300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>571800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>691000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>797600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>465500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>746400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1314900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1613100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1327800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1241900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1150000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1358600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1050100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>965800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>885700</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>325900</v>
+        <v>399200</v>
       </c>
       <c r="E9" s="3">
-        <v>315500</v>
+        <v>318200</v>
       </c>
       <c r="F9" s="3">
-        <v>283400</v>
+        <v>310000</v>
       </c>
       <c r="G9" s="3">
-        <v>347800</v>
+        <v>283500</v>
       </c>
       <c r="H9" s="3">
-        <v>282900</v>
+        <v>338100</v>
       </c>
       <c r="I9" s="3">
-        <v>230800</v>
+        <v>276700</v>
       </c>
       <c r="J9" s="3">
+        <v>238300</v>
+      </c>
+      <c r="K9" s="3">
         <v>169000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>175600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>135700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>147300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>154400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>168500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>173800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>143900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>126700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>150300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>128500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>192500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>272600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>332100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>274700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>256900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>246400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>289200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>210800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>178500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>152200</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1474700</v>
+        <v>1863700</v>
       </c>
       <c r="E10" s="3">
-        <v>1362900</v>
+        <v>1439400</v>
       </c>
       <c r="F10" s="3">
-        <v>1172200</v>
+        <v>1338800</v>
       </c>
       <c r="G10" s="3">
-        <v>1589300</v>
+        <v>1172600</v>
       </c>
       <c r="H10" s="3">
-        <v>1302700</v>
+        <v>1545000</v>
       </c>
       <c r="I10" s="3">
-        <v>1065900</v>
+        <v>1274100</v>
       </c>
       <c r="J10" s="3">
+        <v>1100700</v>
+      </c>
+      <c r="K10" s="3">
         <v>539700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>776600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>421900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>420000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>492000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>567800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>663400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>427900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>564300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>647400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>337000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>553900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1042300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1281000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1053100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>985000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>903600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1069500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>839400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>787300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>733500</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,94 +1084,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>422000</v>
+        <v>518900</v>
       </c>
       <c r="E12" s="3">
-        <v>438300</v>
+        <v>411900</v>
       </c>
       <c r="F12" s="3">
-        <v>411100</v>
+        <v>430600</v>
       </c>
       <c r="G12" s="3">
-        <v>504300</v>
+        <v>411200</v>
       </c>
       <c r="H12" s="3">
-        <v>416300</v>
+        <v>490200</v>
       </c>
       <c r="I12" s="3">
-        <v>377000</v>
+        <v>407200</v>
       </c>
       <c r="J12" s="3">
+        <v>389300</v>
+      </c>
+      <c r="K12" s="3">
         <v>296600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>344200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>246300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>272600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>308700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>317600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>316400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>309700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>301000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>293200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>265400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>267600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>425000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>429600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>403600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>387000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>413500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>361800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>323000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>309900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>297600</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1243,31 +1260,34 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-181900</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>59900</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-101700</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>68400</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-25400</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>324200</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-249800</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1329,31 +1349,34 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>28800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>28900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>28700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>29900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>30100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1415,8 +1438,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1470,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1299400</v>
+        <v>1549200</v>
       </c>
       <c r="E17" s="3">
-        <v>1211000</v>
+        <v>1268400</v>
       </c>
       <c r="F17" s="3">
-        <v>1145900</v>
+        <v>1189700</v>
       </c>
       <c r="G17" s="3">
-        <v>1386000</v>
+        <v>1146300</v>
       </c>
       <c r="H17" s="3">
-        <v>1165900</v>
+        <v>1347300</v>
       </c>
       <c r="I17" s="3">
-        <v>980800</v>
+        <v>1140300</v>
       </c>
       <c r="J17" s="3">
+        <v>1012800</v>
+      </c>
+      <c r="K17" s="3">
         <v>742500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>834200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>580800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>616900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>743600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>770200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>790900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>681400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>693200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>682300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>566900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>984400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1223400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1267900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1124200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1107300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1178800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1143700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>946300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>881100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>842200</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>501200</v>
+        <v>713700</v>
       </c>
       <c r="E18" s="3">
-        <v>467300</v>
+        <v>489200</v>
       </c>
       <c r="F18" s="3">
-        <v>309700</v>
+        <v>459100</v>
       </c>
       <c r="G18" s="3">
-        <v>551100</v>
+        <v>309800</v>
       </c>
       <c r="H18" s="3">
-        <v>419700</v>
+        <v>535700</v>
       </c>
       <c r="I18" s="3">
-        <v>315900</v>
+        <v>410500</v>
       </c>
       <c r="J18" s="3">
+        <v>326200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-33800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>118000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-49600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-97200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-33900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>46300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-109600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>115400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-101400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-238100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>91500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>345200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>203700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>134600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-28800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>214900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>103900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>84700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>43500</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1648,117 +1681,121 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>63600</v>
+        <v>-151500</v>
       </c>
       <c r="E20" s="3">
-        <v>190500</v>
+        <v>-184500</v>
       </c>
       <c r="F20" s="3">
-        <v>-43700</v>
+        <v>-117300</v>
       </c>
       <c r="G20" s="3">
-        <v>153400</v>
+        <v>34400</v>
       </c>
       <c r="H20" s="3">
-        <v>-204100</v>
+        <v>-134000</v>
       </c>
       <c r="I20" s="3">
-        <v>295100</v>
+        <v>-86300</v>
       </c>
       <c r="J20" s="3">
+        <v>28700</v>
+      </c>
+      <c r="K20" s="3">
         <v>437900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>140800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-16000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>14200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-53400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>407300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>166800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>242600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>349100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-522800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>364600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-129300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-129900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>776300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-80500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-305600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>370200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>125800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>96600</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>16</v>
+      <c r="D21" s="3">
+        <v>894200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>702500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>605400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>304100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>699600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>526900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>326800</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>16</v>
@@ -1793,12 +1830,12 @@
       <c r="U21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W21" s="3">
         <v>629000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1820,266 +1857,278 @@
       <c r="AD21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E22" s="3">
+        <v>70700</v>
+      </c>
+      <c r="F22" s="3">
+        <v>69100</v>
+      </c>
+      <c r="G22" s="3">
+        <v>70100</v>
+      </c>
+      <c r="H22" s="3">
         <v>72500</v>
       </c>
-      <c r="E22" s="3">
-        <v>70300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>70100</v>
-      </c>
-      <c r="G22" s="3">
-        <v>74600</v>
-      </c>
-      <c r="H22" s="3">
-        <v>78200</v>
-      </c>
       <c r="I22" s="3">
-        <v>68500</v>
+        <v>76500</v>
       </c>
       <c r="J22" s="3">
+        <v>70800</v>
+      </c>
+      <c r="K22" s="3">
         <v>46500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>68000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>48800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>47100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P22" s="3">
         <v>117700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>59400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>56700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>52500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>62800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>67900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>70700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>61100</v>
-      </c>
-      <c r="W22" s="3">
-        <v>65100</v>
       </c>
       <c r="X22" s="3">
         <v>65100</v>
       </c>
       <c r="Y22" s="3">
+        <v>65100</v>
+      </c>
+      <c r="Z22" s="3">
         <v>67100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>64200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>57100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>53200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>46200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>492300</v>
+        <v>1075500</v>
       </c>
       <c r="E23" s="3">
-        <v>587500</v>
+        <v>630400</v>
       </c>
       <c r="F23" s="3">
-        <v>196000</v>
+        <v>690900</v>
       </c>
       <c r="G23" s="3">
-        <v>629900</v>
+        <v>245500</v>
       </c>
       <c r="H23" s="3">
-        <v>137300</v>
+        <v>697000</v>
       </c>
       <c r="I23" s="3">
-        <v>542500</v>
+        <v>166800</v>
       </c>
       <c r="J23" s="3">
+        <v>540800</v>
+      </c>
+      <c r="K23" s="3">
         <v>357500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>58000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>68800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-112700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-101900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-137400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-66500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>241100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>112100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>295100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>179800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-831600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>395000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>150700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>843800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-173400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-147700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>420800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>164300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>93500</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>97700</v>
+        <v>102800</v>
       </c>
       <c r="E24" s="3">
-        <v>93600</v>
+        <v>95400</v>
       </c>
       <c r="F24" s="3">
+        <v>92000</v>
+      </c>
+      <c r="G24" s="3">
         <v>56300</v>
       </c>
-      <c r="G24" s="3">
-        <v>63200</v>
-      </c>
       <c r="H24" s="3">
-        <v>79200</v>
+        <v>61400</v>
       </c>
       <c r="I24" s="3">
-        <v>48100</v>
+        <v>77500</v>
       </c>
       <c r="J24" s="3">
+        <v>49600</v>
+      </c>
+      <c r="K24" s="3">
         <v>34700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>38300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>24100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>13100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>22700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>35800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>29600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-40100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>57400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>56200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>51300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>103000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>37300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>46200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>25700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2213,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>394600</v>
+        <v>972700</v>
       </c>
       <c r="E26" s="3">
-        <v>493900</v>
+        <v>535000</v>
       </c>
       <c r="F26" s="3">
-        <v>139700</v>
+        <v>599000</v>
       </c>
       <c r="G26" s="3">
-        <v>566700</v>
+        <v>189300</v>
       </c>
       <c r="H26" s="3">
-        <v>58100</v>
+        <v>635600</v>
       </c>
       <c r="I26" s="3">
-        <v>494400</v>
+        <v>89400</v>
       </c>
       <c r="J26" s="3">
+        <v>491200</v>
+      </c>
+      <c r="K26" s="3">
         <v>322800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>44800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-110700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-107000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-150500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-80300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>235400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>89400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>259300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>150200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-791500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>337600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>94500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-42600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>740800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-178700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-185000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>374600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>138600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>540400</v>
+        <v>964400</v>
       </c>
       <c r="E27" s="3">
-        <v>607900</v>
+        <v>527500</v>
       </c>
       <c r="F27" s="3">
-        <v>183000</v>
+        <v>597200</v>
       </c>
       <c r="G27" s="3">
-        <v>650600</v>
+        <v>182900</v>
       </c>
       <c r="H27" s="3">
-        <v>89000</v>
+        <v>632500</v>
       </c>
       <c r="I27" s="3">
-        <v>475800</v>
+        <v>87000</v>
       </c>
       <c r="J27" s="3">
+        <v>491300</v>
+      </c>
+      <c r="K27" s="3">
         <v>290000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>36800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-136600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-115200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-117000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-92000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>247800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>139800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>230400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-70100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-844500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>316800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>122100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-61600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>701700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-181000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-165400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>341600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>152100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2480,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2569,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2658,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2747,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-63600</v>
+        <v>151500</v>
       </c>
       <c r="E32" s="3">
-        <v>-190500</v>
+        <v>184500</v>
       </c>
       <c r="F32" s="3">
-        <v>43700</v>
+        <v>117300</v>
       </c>
       <c r="G32" s="3">
-        <v>-153400</v>
+        <v>-34400</v>
       </c>
       <c r="H32" s="3">
-        <v>204100</v>
+        <v>134000</v>
       </c>
       <c r="I32" s="3">
-        <v>-295100</v>
+        <v>86300</v>
       </c>
       <c r="J32" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="K32" s="3">
         <v>-437900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-140800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>16000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-14200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>53400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-407300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-166800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-242600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-349100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>522800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-364600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>129300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>129900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-776300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>80500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>305600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-370200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-125800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-96600</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>540400</v>
+        <v>964400</v>
       </c>
       <c r="E33" s="3">
-        <v>607900</v>
+        <v>527500</v>
       </c>
       <c r="F33" s="3">
-        <v>183000</v>
+        <v>597200</v>
       </c>
       <c r="G33" s="3">
-        <v>650600</v>
+        <v>182900</v>
       </c>
       <c r="H33" s="3">
-        <v>89000</v>
+        <v>632500</v>
       </c>
       <c r="I33" s="3">
-        <v>475800</v>
+        <v>87000</v>
       </c>
       <c r="J33" s="3">
+        <v>491300</v>
+      </c>
+      <c r="K33" s="3">
         <v>290000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>36800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-136600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-115200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-117000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-92000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>247800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>139800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>230400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-70100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-844500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>316800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>122100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-61600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>701700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-181000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-165400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>341600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>152100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3014,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>540400</v>
+        <v>964400</v>
       </c>
       <c r="E35" s="3">
-        <v>607900</v>
+        <v>527500</v>
       </c>
       <c r="F35" s="3">
-        <v>183000</v>
+        <v>597200</v>
       </c>
       <c r="G35" s="3">
-        <v>650600</v>
+        <v>182900</v>
       </c>
       <c r="H35" s="3">
-        <v>89000</v>
+        <v>632500</v>
       </c>
       <c r="I35" s="3">
-        <v>475800</v>
+        <v>87000</v>
       </c>
       <c r="J35" s="3">
+        <v>491300</v>
+      </c>
+      <c r="K35" s="3">
         <v>290000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>36800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-136600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-115200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-117000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-92000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>247800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>139800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>230400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-70100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-844500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>316800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>122100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-61600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>701700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-181000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-165400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>341600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>152100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3232,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,289 +3265,299 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7267900</v>
+        <v>5985000</v>
       </c>
       <c r="E41" s="3">
-        <v>6312100</v>
+        <v>7094200</v>
       </c>
       <c r="F41" s="3">
-        <v>5863600</v>
+        <v>5842700</v>
       </c>
       <c r="G41" s="3">
-        <v>5323500</v>
+        <v>5865500</v>
       </c>
       <c r="H41" s="3">
-        <v>5194100</v>
+        <v>5175200</v>
       </c>
       <c r="I41" s="3">
-        <v>4310600</v>
+        <v>5080200</v>
       </c>
       <c r="J41" s="3">
+        <v>4451200</v>
+      </c>
+      <c r="K41" s="3">
         <v>2396700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2613400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3191800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2880500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2736500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2828300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3937000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3210000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2519000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3680700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2784500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3800900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3143100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2822500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3514200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3454300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3275100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3121000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3162400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2475500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2617500</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>5387700</v>
+        <v>4892200</v>
       </c>
       <c r="E42" s="3">
-        <v>3596000</v>
+        <v>5258900</v>
       </c>
       <c r="F42" s="3">
-        <v>2502100</v>
+        <v>3532600</v>
       </c>
       <c r="G42" s="3">
-        <v>3394200</v>
+        <v>2502900</v>
       </c>
       <c r="H42" s="3">
-        <v>2612600</v>
+        <v>3299600</v>
       </c>
       <c r="I42" s="3">
-        <v>2451100</v>
+        <v>2555300</v>
       </c>
       <c r="J42" s="3">
+        <v>2531000</v>
+      </c>
+      <c r="K42" s="3">
         <v>3601300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3963000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4270800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4193400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4082500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5081700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5015900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4270500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3454900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3245400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3519800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3955500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3637600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>4014100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>5033900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>5126900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>5590900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>5488700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>4760400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>4896000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>4036100</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1819600</v>
+        <v>1972900</v>
       </c>
       <c r="E43" s="3">
-        <v>1727100</v>
+        <v>1776100</v>
       </c>
       <c r="F43" s="3">
-        <v>2009200</v>
+        <v>2119800</v>
       </c>
       <c r="G43" s="3">
-        <v>1810900</v>
+        <v>2673700</v>
       </c>
       <c r="H43" s="3">
-        <v>1506900</v>
+        <v>1760400</v>
       </c>
       <c r="I43" s="3">
-        <v>1305100</v>
+        <v>1473900</v>
       </c>
       <c r="J43" s="3">
+        <v>1347600</v>
+      </c>
+      <c r="K43" s="3">
         <v>1019800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>849800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>757000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>549400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>871800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>718200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>758900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>605900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>824200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>844600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>755800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>804300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1647000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1431200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1577500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>929100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1112000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>987100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>898300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>742900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>735000</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3523,438 +3619,456 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2659300</v>
+        <v>3487200</v>
       </c>
       <c r="E45" s="3">
-        <v>2466600</v>
+        <v>2595700</v>
       </c>
       <c r="F45" s="3">
-        <v>2134400</v>
+        <v>2000000</v>
       </c>
       <c r="G45" s="3">
-        <v>2668300</v>
+        <v>1110400</v>
       </c>
       <c r="H45" s="3">
-        <v>2400600</v>
+        <v>2593900</v>
       </c>
       <c r="I45" s="3">
-        <v>2138200</v>
+        <v>2347900</v>
       </c>
       <c r="J45" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="K45" s="3">
         <v>1643300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1836700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1498400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1280600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1437400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1925100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1475100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1362200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1277000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1835500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2296300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1638200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2292900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3369700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2122000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2560200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2099400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2669900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1838400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1400500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1190300</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>17134600</v>
+        <v>16337300</v>
       </c>
       <c r="E46" s="3">
-        <v>14101800</v>
+        <v>16725000</v>
       </c>
       <c r="F46" s="3">
-        <v>12509400</v>
+        <v>13853200</v>
       </c>
       <c r="G46" s="3">
-        <v>13197000</v>
+        <v>12513500</v>
       </c>
       <c r="H46" s="3">
-        <v>11714300</v>
+        <v>12829100</v>
       </c>
       <c r="I46" s="3">
-        <v>10205000</v>
+        <v>11457300</v>
       </c>
       <c r="J46" s="3">
+        <v>10537800</v>
+      </c>
+      <c r="K46" s="3">
         <v>8661100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9262900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9717900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8903800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9128200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10553400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11186900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>9448600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8075100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9606100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9356500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10198900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10720600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11637500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12247600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12070600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12077400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12266700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10659600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9514900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8525300</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6399400</v>
+        <v>6664100</v>
       </c>
       <c r="E47" s="3">
-        <v>6720800</v>
+        <v>6246400</v>
       </c>
       <c r="F47" s="3">
-        <v>6959800</v>
+        <v>6602300</v>
       </c>
       <c r="G47" s="3">
-        <v>7537500</v>
+        <v>6958500</v>
       </c>
       <c r="H47" s="3">
-        <v>7719600</v>
+        <v>7327400</v>
       </c>
       <c r="I47" s="3">
-        <v>7996400</v>
+        <v>7550300</v>
       </c>
       <c r="J47" s="3">
+        <v>8257100</v>
+      </c>
+      <c r="K47" s="3">
         <v>7077500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6494100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6127300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5891600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6211700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5954300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6686600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6715800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6677100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7448000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7907200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8101400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8096900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7340700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>5350800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5212700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4122900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3724400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3907000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3652100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3737400</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>821100</v>
+        <v>825700</v>
       </c>
       <c r="E48" s="3">
-        <v>807800</v>
+        <v>801400</v>
       </c>
       <c r="F48" s="3">
-        <v>815300</v>
+        <v>793600</v>
       </c>
       <c r="G48" s="3">
-        <v>820400</v>
+        <v>815600</v>
       </c>
       <c r="H48" s="3">
-        <v>832800</v>
+        <v>797500</v>
       </c>
       <c r="I48" s="3">
-        <v>831400</v>
+        <v>814500</v>
       </c>
       <c r="J48" s="3">
+        <v>858500</v>
+      </c>
+      <c r="K48" s="3">
         <v>849100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>842100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>866400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>841700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>871400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>888100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>940900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>949500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>942000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>973700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>999100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1145700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1158300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1073400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1059800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1013900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>893200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>847700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>835300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>830000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>805800</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>10141000</v>
+        <v>10524500</v>
       </c>
       <c r="E49" s="3">
-        <v>10146800</v>
+        <v>9898600</v>
       </c>
       <c r="F49" s="3">
-        <v>10152800</v>
+        <v>9967900</v>
       </c>
       <c r="G49" s="3">
-        <v>10158200</v>
+        <v>10156100</v>
       </c>
       <c r="H49" s="3">
-        <v>10167500</v>
+        <v>9875000</v>
       </c>
       <c r="I49" s="3">
-        <v>10167600</v>
+        <v>9944400</v>
       </c>
       <c r="J49" s="3">
+        <v>10499200</v>
+      </c>
+      <c r="K49" s="3">
         <v>10173400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9972700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10044900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9989300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9996900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9984200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10310100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10103600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10119400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10649200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10705900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>11274500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11291200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10976900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10908600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10878900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10928800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10452200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10276000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>10086500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10056900</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4153,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,94 +4242,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>442100</v>
+        <v>77700</v>
       </c>
       <c r="E52" s="3">
-        <v>437600</v>
+        <v>74000</v>
       </c>
       <c r="F52" s="3">
-        <v>456600</v>
+        <v>86300</v>
       </c>
       <c r="G52" s="3">
-        <v>361600</v>
+        <v>97000</v>
       </c>
       <c r="H52" s="3">
-        <v>329900</v>
+        <v>88100</v>
       </c>
       <c r="I52" s="3">
-        <v>283200</v>
+        <v>86000</v>
       </c>
       <c r="J52" s="3">
+        <v>86800</v>
+      </c>
+      <c r="K52" s="3">
         <v>263500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>272500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>300700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>307500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>283800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>295000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>301200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>266400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>251400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>265900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>281600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>311100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>311700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>242200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>266800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>217700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>246100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>211200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>240300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>190500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>186800</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,94 +4420,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>34938100</v>
+        <v>34827900</v>
       </c>
       <c r="E54" s="3">
-        <v>32214800</v>
+        <v>34103000</v>
       </c>
       <c r="F54" s="3">
-        <v>30893900</v>
+        <v>31646800</v>
       </c>
       <c r="G54" s="3">
-        <v>32074600</v>
+        <v>30904000</v>
       </c>
       <c r="H54" s="3">
-        <v>30764100</v>
+        <v>31180500</v>
       </c>
       <c r="I54" s="3">
-        <v>29483600</v>
+        <v>30089200</v>
       </c>
       <c r="J54" s="3">
+        <v>30445000</v>
+      </c>
+      <c r="K54" s="3">
         <v>27024600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>26844200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27057200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25933900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26491900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27675000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29425800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>27483900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26065100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>28943000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>29250200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>31031500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>31578700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>31270700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>29833700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>29393700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>28268500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>27502200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>25918200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>24274100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>23278200</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4544,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,524 +4577,543 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2705300</v>
+        <v>2508500</v>
       </c>
       <c r="E57" s="3">
-        <v>2500400</v>
+        <v>2640600</v>
       </c>
       <c r="F57" s="3">
-        <v>2320400</v>
+        <v>2490800</v>
       </c>
       <c r="G57" s="3">
-        <v>2562000</v>
+        <v>2363900</v>
       </c>
       <c r="H57" s="3">
-        <v>2076500</v>
+        <v>2490600</v>
       </c>
       <c r="I57" s="3">
-        <v>1591200</v>
+        <v>2030900</v>
       </c>
       <c r="J57" s="3">
+        <v>1643100</v>
+      </c>
+      <c r="K57" s="3">
         <v>1067100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1020900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>937700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>580100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>831100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1009200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>934900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>692200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>627200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1038100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>659900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>777600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1939500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2061200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1974700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1668600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1781900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1975000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1593800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1351000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1070200</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5572900</v>
+        <v>3793100</v>
       </c>
       <c r="E58" s="3">
-        <v>5445600</v>
+        <v>5439700</v>
       </c>
       <c r="F58" s="3">
-        <v>3645300</v>
+        <v>5349600</v>
       </c>
       <c r="G58" s="3">
-        <v>4343200</v>
+        <v>3666200</v>
       </c>
       <c r="H58" s="3">
-        <v>4569700</v>
+        <v>4222100</v>
       </c>
       <c r="I58" s="3">
-        <v>5530800</v>
+        <v>4469500</v>
       </c>
       <c r="J58" s="3">
+        <v>5711100</v>
+      </c>
+      <c r="K58" s="3">
         <v>4606400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4679200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5032900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4262500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5504700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6219800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5823500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5678800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4686200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5012900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6203400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6370700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4814200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5658900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5758300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5769000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5478000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5232100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3509800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2952200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2341000</v>
       </c>
     </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4708300</v>
+        <v>5165600</v>
       </c>
       <c r="E59" s="3">
-        <v>4292000</v>
+        <v>4595800</v>
       </c>
       <c r="F59" s="3">
-        <v>4242800</v>
+        <v>3380500</v>
       </c>
       <c r="G59" s="3">
-        <v>4339100</v>
+        <v>2468000</v>
       </c>
       <c r="H59" s="3">
-        <v>4022700</v>
+        <v>4218100</v>
       </c>
       <c r="I59" s="3">
-        <v>3387600</v>
+        <v>3934500</v>
       </c>
       <c r="J59" s="3">
+        <v>3498100</v>
+      </c>
+      <c r="K59" s="3">
         <v>2960000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2825500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2745400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2588300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2807600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2900100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2988800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2765800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2811600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2909400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2944500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3547900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4160400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3692600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3668900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3135500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3203500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2823300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2821200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2478900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2698200</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>12986500</v>
+        <v>11467200</v>
       </c>
       <c r="E60" s="3">
-        <v>12238100</v>
+        <v>12676100</v>
       </c>
       <c r="F60" s="3">
-        <v>10208500</v>
+        <v>12022300</v>
       </c>
       <c r="G60" s="3">
-        <v>11244300</v>
+        <v>10211800</v>
       </c>
       <c r="H60" s="3">
-        <v>10668900</v>
+        <v>10930800</v>
       </c>
       <c r="I60" s="3">
-        <v>10509600</v>
+        <v>10434900</v>
       </c>
       <c r="J60" s="3">
+        <v>10852400</v>
+      </c>
+      <c r="K60" s="3">
         <v>8633500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8525600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8716000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7430900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9143400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10129200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9747200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9136800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8125000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8960400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9807800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10696100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10914200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11412700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11401800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10573100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10463400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10030300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7924800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6782200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6049400</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2824400</v>
+        <v>2804000</v>
       </c>
       <c r="E61" s="3">
-        <v>1224800</v>
+        <v>2831900</v>
       </c>
       <c r="F61" s="3">
-        <v>2692600</v>
+        <v>1268100</v>
       </c>
       <c r="G61" s="3">
-        <v>2774100</v>
+        <v>2760700</v>
       </c>
       <c r="H61" s="3">
-        <v>2776900</v>
+        <v>2760900</v>
       </c>
       <c r="I61" s="3">
-        <v>1896600</v>
+        <v>2782700</v>
       </c>
       <c r="J61" s="3">
+        <v>2030900</v>
+      </c>
+      <c r="K61" s="3">
         <v>1857700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2408800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2419200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2803300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1531700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1690700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3228700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3251200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3162300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4710800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4136000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3674500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3082200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3172000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3311200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3721600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3673100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3785000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4291800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4171300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4192500</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>603500</v>
+        <v>38500</v>
       </c>
       <c r="E62" s="3">
-        <v>620600</v>
+        <v>35600</v>
       </c>
       <c r="F62" s="3">
-        <v>651500</v>
+        <v>45100</v>
       </c>
       <c r="G62" s="3">
-        <v>629500</v>
+        <v>45000</v>
       </c>
       <c r="H62" s="3">
-        <v>626100</v>
+        <v>49600</v>
       </c>
       <c r="I62" s="3">
-        <v>598600</v>
+        <v>42700</v>
       </c>
       <c r="J62" s="3">
+        <v>38300</v>
+      </c>
+      <c r="K62" s="3">
         <v>600000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>581900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>591100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>555800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>565000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>571400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>624300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>649400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>639600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>627800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>635000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>725400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>726500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>698100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>683800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>748700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>633900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>618100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>649800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>592000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>608800</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5198,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5287,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,94 +5376,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>16540200</v>
+        <v>14851100</v>
       </c>
       <c r="E66" s="3">
-        <v>14201200</v>
+        <v>16022100</v>
       </c>
       <c r="F66" s="3">
-        <v>13668400</v>
+        <v>13835200</v>
       </c>
       <c r="G66" s="3">
-        <v>14759300</v>
+        <v>13557000</v>
       </c>
       <c r="H66" s="3">
-        <v>14177900</v>
+        <v>14239500</v>
       </c>
       <c r="I66" s="3">
-        <v>13108700</v>
+        <v>13763200</v>
       </c>
       <c r="J66" s="3">
+        <v>13428900</v>
+      </c>
+      <c r="K66" s="3">
         <v>11194900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11614800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11828700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10895200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11347700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12518600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13733100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13169000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12095800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14527600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14878300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15631500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15259700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15770800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15766100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15412600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15077400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14757400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13139500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>11814400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>11105900</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5500,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5587,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5676,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5765,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,8 +5854,11 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5695,10 +5869,10 @@
         <v>16</v>
       </c>
       <c r="F72" s="3">
-        <v>4353200</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>16</v>
+        <v>4873600</v>
+      </c>
+      <c r="G72" s="3">
+        <v>4354600</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>16</v>
@@ -5706,71 +5880,74 @@
       <c r="I72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K72" s="3">
         <v>2954900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O72" s="3">
         <v>2700400</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S72" s="3">
         <v>2798900</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W72" s="3">
         <v>3697600</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y72" s="3">
         <v>3152900</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA72" s="3">
         <v>2498900</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD72" s="3">
         <v>2379000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2227000</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6032,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6121,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,94 +6210,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>18397900</v>
+        <v>19836500</v>
       </c>
       <c r="E76" s="3">
-        <v>18013600</v>
+        <v>17958100</v>
       </c>
       <c r="F76" s="3">
-        <v>17225500</v>
+        <v>17696000</v>
       </c>
       <c r="G76" s="3">
-        <v>17315300</v>
+        <v>17231100</v>
       </c>
       <c r="H76" s="3">
-        <v>16586200</v>
+        <v>16832600</v>
       </c>
       <c r="I76" s="3">
-        <v>16374800</v>
+        <v>16222300</v>
       </c>
       <c r="J76" s="3">
+        <v>16908800</v>
+      </c>
+      <c r="K76" s="3">
         <v>15829700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15229400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15228500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15038700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15144200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15156500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15692600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14314900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13969300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14415400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14371900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15400100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16319000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15499900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14067500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13981000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13191100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12744800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12778800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12459700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12172300</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6388,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>540400</v>
+        <v>964400</v>
       </c>
       <c r="E81" s="3">
-        <v>607900</v>
+        <v>527500</v>
       </c>
       <c r="F81" s="3">
-        <v>183000</v>
+        <v>597200</v>
       </c>
       <c r="G81" s="3">
-        <v>650600</v>
+        <v>182900</v>
       </c>
       <c r="H81" s="3">
-        <v>89000</v>
+        <v>632500</v>
       </c>
       <c r="I81" s="3">
-        <v>475800</v>
+        <v>87000</v>
       </c>
       <c r="J81" s="3">
+        <v>491300</v>
+      </c>
+      <c r="K81" s="3">
         <v>290000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>36800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-136600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-115200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-117000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-92000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>247800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>139800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>230400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-70100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-844500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>316800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>122100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-61600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>701700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-181000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-165400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>341600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>152100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,31 +6606,32 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>36700</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -6464,15 +6663,15 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W83" s="3">
         <v>172900</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
       <c r="X83" s="3">
         <v>0</v>
       </c>
@@ -6494,8 +6693,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6782,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6871,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6960,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7049,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,31 +7138,34 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
+        <v>339700</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>462200</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -6980,15 +7197,15 @@
       <c r="T89" s="3">
         <v>0</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W89" s="3">
         <v>1156900</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
         <v>0</v>
       </c>
@@ -7010,8 +7227,11 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,31 +7262,32 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+        <v>-16900</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-16200</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -7098,15 +7319,15 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W91" s="3">
         <v>-129800</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
@@ -7128,8 +7349,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7438,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,31 +7527,34 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
+        <v>-602600</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>334200</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -7356,15 +7586,15 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W94" s="3">
         <v>-380700</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
@@ -7386,8 +7616,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,31 +7651,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7504,8 +7738,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7827,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7916,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,31 +8005,34 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
+        <v>328100</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>946400</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -7818,15 +8064,15 @@
       <c r="T100" s="3">
         <v>0</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W100" s="3">
         <v>-1460200</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -7848,31 +8094,34 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+        <v>17000</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7904,15 +8153,15 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W101" s="3">
         <v>48700</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
@@ -7934,8 +8183,11 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7946,7 +8198,7 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>0</v>
+        <v>109400</v>
       </c>
       <c r="G102" s="3">
         <v>0</v>
@@ -7958,7 +8210,7 @@
         <v>0</v>
       </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>1759900</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -7990,15 +8242,15 @@
       <c r="T102" s="3">
         <v>0</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W102" s="3">
         <v>-635300</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
       <c r="X102" s="3">
         <v>0</v>
       </c>
@@ -8018,6 +8270,9 @@
         <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TCOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TCOM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>TCOM</t>
   </si>
@@ -656,404 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1746000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2262900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1757600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1648800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1456100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1883100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1550800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1339000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>708700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>952200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>557600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>567400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>646400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>736300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>837300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>571800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>691000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>797600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>465500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>746400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1314900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1613100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1327800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1241900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1150000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1358600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1050100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>965800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>885700</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>361700</v>
+      </c>
+      <c r="E9" s="3">
         <v>399200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>318200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>310000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>283500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>338100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>276700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>238300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>169000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>175600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>135700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>147300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>154400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>168500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>173800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>143900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>126700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>150300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>128500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>192500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>272600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>332100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>274700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>256900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>246400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>289200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>210800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>178500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>152200</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1384300</v>
+      </c>
+      <c r="E10" s="3">
         <v>1863700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1439400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1338800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1172600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1545000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1274100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1100700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>539700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>776600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>421900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>420000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>492000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>567800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>663400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>427900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>564300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>647400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>337000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>553900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1042300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1281000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1053100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>985000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>903600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1069500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>839400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>787300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>733500</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1085,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>465400</v>
+      </c>
+      <c r="E12" s="3">
         <v>518900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>411900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>430600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>411200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>490200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>407200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>389300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>296600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>344200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>246300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>272600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>308700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>317600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>316400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>309700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>301000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>293200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>265400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>267600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>425000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>429600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>403600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>387000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>413500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>361800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>323000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>309900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>297600</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1263,35 +1279,38 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-181900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>59900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-101700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>68400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-25400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>324200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-249800</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1352,35 +1371,38 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E15" s="3">
         <v>29000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>28800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>28900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>28700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>29900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>30100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>29300</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1441,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1430700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1549200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1268400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1189700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1146300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1347300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1140300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1012800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>742500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>834200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>580800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>616900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>743600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>770200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>790900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>681400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>693200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>682300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>566900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>984400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1223400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1267900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1124200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1107300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1178800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1143700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>946300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>881100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>842200</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>315200</v>
+      </c>
+      <c r="E18" s="3">
         <v>713700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>489200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>459100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>309800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>535700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>410500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>326200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-33800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>118000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-23200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-49600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-97200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-33900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>46300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-109600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>115400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-101400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-238100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>91500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>345200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>203700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>134600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-28800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>214900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>103900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>84700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>43500</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1682,124 +1714,128 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-90400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-151500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-184500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-117300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>34400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-134000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-86300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>28700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>437900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>140800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-16000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>14200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-53400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>407300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>166800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>242600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>349100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-522800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>364600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-129300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-129900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>776300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-80500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-305600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>370200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>125800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>96600</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>433500</v>
+      </c>
+      <c r="E21" s="3">
         <v>894200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>702500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>605400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>304100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>699600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>526900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>326800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1833,12 +1869,12 @@
       <c r="V21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X21" s="3">
         <v>629000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1860,275 +1896,287 @@
       <c r="AE21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E22" s="3">
         <v>56900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>70700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>69100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>70100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>72500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>76500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>70800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>46500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>68000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>48800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>47100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q22" s="3">
         <v>117700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>59400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>56700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>52500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>62800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>67900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>70700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>61100</v>
-      </c>
-      <c r="X22" s="3">
-        <v>65100</v>
       </c>
       <c r="Y22" s="3">
         <v>65100</v>
       </c>
       <c r="Z22" s="3">
+        <v>65100</v>
+      </c>
+      <c r="AA22" s="3">
         <v>67100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>64200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>57100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>53200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>46200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>372200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1075500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>630400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>690900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>245500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>697000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>166800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>540800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>357500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>58000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>68800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-112700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-101900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-137400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-66500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>241100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>112100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>295100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>179800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-831600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>395000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>150700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>843800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-173400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-147700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>420800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>164300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>93500</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E24" s="3">
         <v>102800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>95400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>92000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>56300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>61400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>77500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>49600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>34700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>38300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>24100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>13800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>22700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>35800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>29600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-40100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>57400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>56200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>51300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>103000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>37300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>46200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>25700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>300200</v>
+      </c>
+      <c r="E26" s="3">
         <v>972700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>535000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>599000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>189300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>635600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>89400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>491200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>322800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>44800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-110700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-107000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-150500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-80300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>235400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>89400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>259300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>150200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-791500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>337600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>94500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-42600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>740800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-178700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-185000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>374600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>138600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>295500</v>
+      </c>
+      <c r="E27" s="3">
         <v>964400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>527500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>597200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>182900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>632500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>87000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>491300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>290000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>36800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-136600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-115200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-117000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-92000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>247800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>139800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>230400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-70100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-844500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>316800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>122100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-61600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>701700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-181000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-165400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>341600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>152100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,186 +2816,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>90400</v>
+      </c>
+      <c r="E32" s="3">
         <v>151500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>184500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>117300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-34400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>134000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>86300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-28700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-437900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-140800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>16000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>53400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-407300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-166800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-242600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-349100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>522800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-364600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>129300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>129900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-776300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>80500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>305600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-370200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-125800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-96600</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>295500</v>
+      </c>
+      <c r="E33" s="3">
         <v>964400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>527500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>597200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>182900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>632500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>87000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>491300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>290000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>36800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-136600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-115200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-117000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-92000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>247800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>139800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>230400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-70100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-844500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>316800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>122100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-61600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>701700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-181000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-165400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>341600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>152100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>295500</v>
+      </c>
+      <c r="E35" s="3">
         <v>964400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>527500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>597200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>182900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>632500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>87000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>491300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>290000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>36800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-136600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-115200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-117000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-92000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>247800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>139800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>230400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-70100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-844500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>316800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>122100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-61600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>701700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-181000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-165400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>341600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>152100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,275 +3351,285 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6999900</v>
+      </c>
+      <c r="E41" s="3">
         <v>5985000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7094200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5842700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5865500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5175200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5080200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4451200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2396700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2613400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3191800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2880500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2736500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2828300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3937000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3210000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2519000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3680700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2784500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3800900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3143100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2822500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3514200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3454300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3275100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3121000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3162400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2475500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2617500</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3901200</v>
+      </c>
+      <c r="E42" s="3">
         <v>4892200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5258900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3532600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2502900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3299600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2555300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2531000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3601300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3963000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4270800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4193400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4082500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5081700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5015900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4270500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3454900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3245400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3519800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3955500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3637600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>4014100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>5033900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>5126900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>5590900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>5488700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>4760400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>4896000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>4036100</v>
       </c>
     </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1706900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1972900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1776100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2119800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2673700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1760400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1473900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1347600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1019800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>849800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>757000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>549400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>871800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>718200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>758900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>605900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>824200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>844600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>755800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>804300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1647000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1431200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1577500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>929100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1112000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>987100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>898300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>742900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>735000</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3559,8 +3654,8 @@
       <c r="J44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3622,453 +3717,471 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2752800</v>
+      </c>
+      <c r="E45" s="3">
         <v>3487200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2595700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2000000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1110400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2593900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2347900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2208000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1643300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1836700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1498400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1280600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1437400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1925100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1475100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1362200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1277000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1835500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2296300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1638200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2292900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3369700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2122000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2560200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2099400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2669900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1838400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1400500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1190300</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15360800</v>
+      </c>
+      <c r="E46" s="3">
         <v>16337300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16725000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13853200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12513500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12829100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11457300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10537800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8661100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9262900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9717900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8903800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9128200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10553400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11186900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9448600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8075100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9606100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9356500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10198900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10720600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11637500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>12247600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12070600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12077400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>12266700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>10659600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9514900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8525300</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6465700</v>
+      </c>
+      <c r="E47" s="3">
         <v>6664100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6246400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6602300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6958500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7327400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7550300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8257100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7077500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6494100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6127300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5891600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6211700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5954300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6686600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6715800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6677100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7448000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7907200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8101400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8096900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7340700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>5350800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5212700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4122900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3724400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3907000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3652100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3737400</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>795700</v>
+      </c>
+      <c r="E48" s="3">
         <v>825700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>801400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>793600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>815600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>797500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>814500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>858500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>849100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>842100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>866400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>841700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>871400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>888100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>940900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>949500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>942000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>973700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>999100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1145700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1158300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1073400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1059800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1013900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>893200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>847700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>835300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>830000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>805800</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10104100</v>
+      </c>
+      <c r="E49" s="3">
         <v>10524500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9898600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9967900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10156100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9875000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9944400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10499200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10173400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9972700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10044900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9989300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9996900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9984200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>10310100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10103600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10119400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10649200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10705900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11274500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>11291200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10976900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10908600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10878900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10928800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10452200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>10276000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10086500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10056900</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,97 +4361,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E52" s="3">
         <v>77700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>74000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>86300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>97000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>88100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>86000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>86800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>263500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>272500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>300700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>307500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>283800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>295000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>301200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>266400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>251400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>265900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>281600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>311100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>311700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>242200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>266800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>217700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>246100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>211200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>240300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>190500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>186800</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33234400</v>
+      </c>
+      <c r="E54" s="3">
         <v>34827900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>34103000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31646800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30904000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>31180500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30089200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>30445000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27024600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26844200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27057200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25933900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26491900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>27675000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29425800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>27483900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26065100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>28943000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>29250200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>31031500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>31578700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>31270700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>29833700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>29393700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>28268500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>27502200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>25918200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>24274100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>23278200</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,542 +4707,561 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2271200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2508500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2640600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2490800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2363900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2490600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2030900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1643100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1067100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1020900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>937700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>580100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>831100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1009200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>934900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>692200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>627200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1038100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>659900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>777600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1939500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2061200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1974700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1668600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1781900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1975000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1593800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1351000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1070200</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2662400</v>
+      </c>
+      <c r="E58" s="3">
         <v>3793100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5439700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5349600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3666200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4222100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4469500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5711100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4606400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4679200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5032900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4262500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5504700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6219800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5823500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5678800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4686200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5012900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6203400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6370700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4814200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5658900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5758300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5769000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5478000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>5232100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3509800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2952200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2341000</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5206000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5165600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4595800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3380500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2468000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4218100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3934500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3498100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2960000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2825500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2745400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2588300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2807600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2900100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2988800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2765800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2811600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2909400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2944500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3547900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4160400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3692600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3668900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3135500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3203500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2823300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2821200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2478900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2698200</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10139600</v>
+      </c>
+      <c r="E60" s="3">
         <v>11467200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12676100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12022300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10211800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10930800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10434900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10852400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8633500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8525600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8716000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7430900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9143400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10129200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9747200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9136800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8125000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8960400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9807800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10696100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10914200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11412700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11401800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10573100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10463400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10030300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7924800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6782200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6049400</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2835300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2804000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2831900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1268100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2760700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2760900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2782700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2030900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1857700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2408800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2419200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2803300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1531700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1690700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3228700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3251200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3162300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4710800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4136000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3674500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3082200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3172000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3311200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3721600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3673100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3785000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4291800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4171300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4192500</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E62" s="3">
         <v>38500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>35600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>45100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>45000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>49600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>42700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>38300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>600000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>581900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>591100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>555800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>565000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>571400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>624300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>649400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>639600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>627800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>635000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>725400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>726500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>698100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>683800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>748700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>633900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>618100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>649800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>592000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>608800</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13576900</v>
+      </c>
+      <c r="E66" s="3">
         <v>14851100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16022100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13835200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13557000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14239500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13763200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13428900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11194900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11614800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11828700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10895200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11347700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12518600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13733100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13169000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12095800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14527600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14878300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15631500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15259700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15770800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15766100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15412600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15077400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14757400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13139500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>11814400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>11105900</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,8 +6027,11 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5868,86 +6041,89 @@
       <c r="E72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G72" s="3">
         <v>4873600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4354600</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L72" s="3">
         <v>2954900</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P72" s="3">
         <v>2700400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T72" s="3">
         <v>2798900</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X72" s="3">
         <v>3697600</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z72" s="3">
         <v>3152900</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB72" s="3">
         <v>2498900</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE72" s="3">
         <v>2379000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2227000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19529800</v>
+      </c>
+      <c r="E76" s="3">
         <v>19836500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17958100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17696000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17231100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16832600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16222300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16908800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15829700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15229400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15228500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15038700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15144200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15156500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15692600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14314900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13969300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14415400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14371900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15400100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16319000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15499900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14067500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13981000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13191100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12744800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12778800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12459700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12172300</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>295500</v>
+      </c>
+      <c r="E81" s="3">
         <v>964400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>527500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>597200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>182900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>632500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>87000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>491300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>290000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>36800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-136600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-115200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-117000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-92000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>247800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>139800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>230400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-70100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-844500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>316800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>122100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-61600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>701700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-181000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-165400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>341600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>152100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6618,12 +6816,12 @@
       <c r="E83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" s="3">
         <v>36700</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>16</v>
       </c>
@@ -6633,8 +6831,8 @@
       <c r="J83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -6666,15 +6864,15 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X83" s="3">
         <v>172900</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
       <c r="Y83" s="3">
         <v>0</v>
       </c>
@@ -6696,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,8 +7354,11 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7152,24 +7368,24 @@
       <c r="E89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G89" s="3">
         <v>339700</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K89" s="3">
         <v>462200</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
         <v>0</v>
       </c>
@@ -7200,15 +7416,15 @@
       <c r="U89" s="3">
         <v>0</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X89" s="3">
         <v>1156900</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
         <v>0</v>
       </c>
@@ -7230,8 +7446,11 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7274,24 +7494,24 @@
       <c r="E91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G91" s="3">
         <v>-16900</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H91" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K91" s="3">
         <v>-16200</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -7322,15 +7542,15 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X91" s="3">
         <v>-129800</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
@@ -7352,8 +7572,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,8 +7756,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7541,24 +7770,24 @@
       <c r="E94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G94" s="3">
         <v>-602600</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K94" s="3">
         <v>334200</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
@@ -7589,15 +7818,15 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X94" s="3">
         <v>-380700</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
@@ -7619,8 +7848,11 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7678,8 +7911,8 @@
       <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7741,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8019,24 +8264,24 @@
       <c r="E100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G100" s="3">
         <v>328100</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K100" s="3">
         <v>946400</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -8067,15 +8312,15 @@
       <c r="U100" s="3">
         <v>0</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X100" s="3">
         <v>-1460200</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
@@ -8097,8 +8342,11 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8108,12 +8356,12 @@
       <c r="E101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G101" s="3">
         <v>17000</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>16</v>
       </c>
@@ -8123,8 +8371,8 @@
       <c r="J101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8156,15 +8404,15 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X101" s="3">
         <v>48700</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
@@ -8186,8 +8434,11 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8198,11 +8449,11 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>109400</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
@@ -8210,11 +8461,11 @@
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>1759900</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
@@ -8245,15 +8496,15 @@
       <c r="U102" s="3">
         <v>0</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X102" s="3">
         <v>-635300</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
         <v>0</v>
       </c>
@@ -8273,6 +8524,9 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TCOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TCOM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>TCOM</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1905900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1746000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2262900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1757600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1648800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1456100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1883100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1550800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1339000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>708700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>952200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>557600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>567400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>646400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>736300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>837300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>571800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>691000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>797600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>465500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>746400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1314900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1613100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1327800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1241900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1150000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1358600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1050100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>965800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>885700</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>372800</v>
+      </c>
+      <c r="E9" s="3">
         <v>361700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>399200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>318200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>310000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>283500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>338100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>276700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>238300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>169000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>175600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>135700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>147300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>154400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>168500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>173800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>143900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>126700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>150300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>128500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>192500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>272600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>332100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>274700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>256900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>246400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>289200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>210800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>178500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>152200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1533100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1384300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1863700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1439400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1338800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1172600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1545000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1274100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1100700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>539700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>776600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>421900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>420000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>492000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>567800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>663400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>427900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>564300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>647400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>337000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>553900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1042300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1281000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1053100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>985000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>903600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1069500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>839400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>787300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>733500</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1111,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>485800</v>
+      </c>
+      <c r="E12" s="3">
         <v>465400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>518900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>411900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>430600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>411200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>490200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>407200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>389300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>296600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>344200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>246300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>272600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>308700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>317600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>316400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>309700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>301000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>293200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>265400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>267600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>425000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>429600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>403600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>387000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>413500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>361800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>323000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>309900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>297600</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,38 +1299,41 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>60000</v>
+        <v>-72500</v>
       </c>
       <c r="E14" s="3">
+        <v>-32700</v>
+      </c>
+      <c r="F14" s="3">
         <v>-181900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>59900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-101700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>68400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-25400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>324200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-249800</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1374,38 +1394,41 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>27900</v>
+        <v>29200</v>
       </c>
       <c r="E15" s="3">
         <v>29000</v>
       </c>
       <c r="F15" s="3">
+        <v>29000</v>
+      </c>
+      <c r="G15" s="3">
         <v>28800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>28900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>28700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>29900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>30100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>29300</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1414900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1430700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1549200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1268400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1189700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1146300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1347300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1140300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1012800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>742500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>834200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>580800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>616900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>743600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>770200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>790900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>681400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>693200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>682300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>566900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>984400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1223400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1267900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1124200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1107300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1178800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1143700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>946300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>881100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>842200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>491000</v>
+      </c>
+      <c r="E18" s="3">
         <v>315200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>713700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>489200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>459100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>309800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>535700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>410500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>326200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-33800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>118000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-23200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-49600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-97200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-33900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>46300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-109600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>115400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-101400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-238100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>91500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>345200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>203700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>134600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-28800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>214900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>103900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>84700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>43500</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1715,130 +1748,134 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-90400</v>
+        <v>-70100</v>
       </c>
       <c r="E20" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F20" s="3">
         <v>-151500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-184500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-117300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>34400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-134000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-86300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>28700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>437900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>140800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-16000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>14200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-53400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>407300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>166800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>242600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>349100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-522800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>364600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-129300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-129900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>776300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-80500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-305600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>370200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>125800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>96600</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>433500</v>
+        <v>590400</v>
       </c>
       <c r="E21" s="3">
+        <v>318700</v>
+      </c>
+      <c r="F21" s="3">
         <v>894200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>702500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>605400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>304100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>699600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>526900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>326800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1872,12 +1909,12 @@
       <c r="W21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y21" s="3">
         <v>629000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1899,284 +1936,296 @@
       <c r="AF21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E22" s="3">
         <v>44300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>56900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>70700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>69100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>70100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>72500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>76500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>70800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>46500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>68000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>48800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>47100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R22" s="3">
         <v>117700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>59400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>56700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>52500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>62800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>67900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>70700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>61100</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>65100</v>
       </c>
       <c r="Z22" s="3">
         <v>65100</v>
       </c>
       <c r="AA22" s="3">
+        <v>65100</v>
+      </c>
+      <c r="AB22" s="3">
         <v>67100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>64200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>57100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>53200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>46200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>682400</v>
+      </c>
+      <c r="E23" s="3">
         <v>372200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1075500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>630400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>690900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>245500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>697000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>166800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>540800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>357500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>58000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>68800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-112700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-101900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-137400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-66500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>241100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>112100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>295100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>179800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-831600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>395000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>150700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>843800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-173400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-147700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>420800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>164300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>93500</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E24" s="3">
         <v>72100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>102800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>95400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>92000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>56300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>61400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>77500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>49600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>34700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>38300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>24100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>13100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>13800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>22700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>35800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>29600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-40100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>57400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>56200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>51300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>103000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>37300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>46200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>25700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>594500</v>
+      </c>
+      <c r="E26" s="3">
         <v>300200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>972700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>535000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>599000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>189300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>635600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>89400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>491200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>322800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>44800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-110700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-107000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-150500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-80300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>235400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>89400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>259300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>150200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-791500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>337600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>94500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>740800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-178700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-185000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>374600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>138600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>589400</v>
+      </c>
+      <c r="E27" s="3">
         <v>295500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>964400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>527500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>597200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>182900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>632500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>87000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>491300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>290000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>36800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-136600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-115200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-117000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-92000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>247800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>139800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>230400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-70100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-844500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>316800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>122100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-61600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>701700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-181000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-165400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>341600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>152100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>90400</v>
+        <v>70100</v>
       </c>
       <c r="E32" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="F32" s="3">
         <v>151500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>184500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>117300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-34400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>134000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>86300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-28700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-437900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-140800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>16000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-14200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>53400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-407300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-166800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-242600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-349100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>522800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-364600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>129300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>129900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-776300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>80500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>305600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-370200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-125800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-96600</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>589400</v>
+      </c>
+      <c r="E33" s="3">
         <v>295500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>964400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>527500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>597200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>182900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>632500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>87000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>491300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>290000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>36800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-136600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-115200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-117000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-92000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>247800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>139800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>230400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-70100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-844500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>316800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>122100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-61600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>701700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-181000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-165400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>341600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>152100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>589400</v>
+      </c>
+      <c r="E35" s="3">
         <v>295500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>964400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>527500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>597200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>182900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>632500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>87000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>491300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>290000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>36800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-136600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-115200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-117000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-92000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>247800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>139800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>230400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-70100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-844500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>316800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>122100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-61600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>701700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-181000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-165400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>341600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>152100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,284 +3438,294 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6999900</v>
+        <v>7766800</v>
       </c>
       <c r="E41" s="3">
+        <v>6636300</v>
+      </c>
+      <c r="F41" s="3">
         <v>5985000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7094200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5842700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5865500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5175200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5080200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4451200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2396700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2613400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3191800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2880500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2736500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2828300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3937000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3210000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2519000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3680700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2784500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3800900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3143100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2822500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3514200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3454300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3275100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3121000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3162400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2475500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2617500</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2995800</v>
+      </c>
+      <c r="E42" s="3">
         <v>3901200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4892200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5258900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3532600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2502900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3299600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2555300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2531000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3601300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3963000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4270800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4193400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4082500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5081700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>5015900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4270500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3454900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3245400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3519800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3955500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3637600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>4014100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>5033900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>5126900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>5590900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>5488700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>4760400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>4896000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>4036100</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1706900</v>
+        <v>1840700</v>
       </c>
       <c r="E43" s="3">
+        <v>2992400</v>
+      </c>
+      <c r="F43" s="3">
         <v>1972900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1776100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2119800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2673700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1760400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1473900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1347600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1019800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>849800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>757000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>549400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>871800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>718200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>758900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>605900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>824200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>844600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>755800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>804300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1647000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1431200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1577500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>929100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1112000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>987100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>898300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>742900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>735000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3657,8 +3753,8 @@
       <c r="K44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3720,468 +3816,486 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2752800</v>
+        <v>2870800</v>
       </c>
       <c r="E45" s="3">
+        <v>1444000</v>
+      </c>
+      <c r="F45" s="3">
         <v>3487200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2595700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2000000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1110400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2593900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2347900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2208000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1643300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1836700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1498400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1280600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1437400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1925100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1475100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1362200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1277000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1835500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2296300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1638200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2292900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3369700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2122000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2560200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2099400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2669900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1838400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1400500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1190300</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15474100</v>
+      </c>
+      <c r="E46" s="3">
         <v>15360800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16337300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16725000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13853200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>12513500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>12829100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11457300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10537800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8661100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9262900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9717900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8903800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9128200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10553400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11186900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9448600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8075100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9606100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9356500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10198900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10720600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11637500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12247600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>12070600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>12077400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>12266700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>10659600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9514900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8525300</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7141900</v>
+      </c>
+      <c r="E47" s="3">
         <v>6465700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6664100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6246400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6602300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6958500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7327400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7550300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8257100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7077500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6494100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6127300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5891600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6211700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5954300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6686600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6715800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>6677100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7448000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7907200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8101400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8096900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7340700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5350800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>5212700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4122900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3724400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3907000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3652100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3737400</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>800900</v>
+      </c>
+      <c r="E48" s="3">
         <v>795700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>825700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>801400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>793600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>815600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>797500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>814500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>858500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>849100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>842100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>866400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>841700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>871400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>888100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>940900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>949500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>942000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>973700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>999100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1145700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1158300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1073400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1059800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1013900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>893200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>847700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>835300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>830000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>805800</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10191600</v>
+      </c>
+      <c r="E49" s="3">
         <v>10104100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10524500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9898600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9967900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10156100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9875000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9944400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10499200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10173400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9972700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10044900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9989300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9996900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9984200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>10310100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10103600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10119400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10649200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10705900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>11274500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>11291200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>10976900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>10908600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10878900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10928800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>10452200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10276000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10086500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10056900</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4481,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E52" s="3">
         <v>62200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>77700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>74000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>86300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>97000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>88100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>86000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>86800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>263500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>272500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>300700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>307500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>283800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>295000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>301200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>266400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>251400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>265900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>281600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>311100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>311700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>242200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>266800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>217700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>246100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>211200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>240300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>190500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>186800</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>34143500</v>
+      </c>
+      <c r="E54" s="3">
         <v>33234400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>34827900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>34103000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31646800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30904000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>31180500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>30089200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>30445000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27024600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26844200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27057200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>25933900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26491900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>27675000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>29425800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>27483900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26065100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>28943000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>29250200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>31031500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>31578700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>31270700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>29833700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>29393700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>28268500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>27502200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>25918200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>24274100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>23278200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4838,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2271200</v>
+        <v>2339800</v>
       </c>
       <c r="E57" s="3">
+        <v>2325600</v>
+      </c>
+      <c r="F57" s="3">
         <v>2508500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2640600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2490800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2363900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2490600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2030900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1643100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1067100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1020900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>937700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>580100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>831100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1009200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>934900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>692200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>627200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1038100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>659900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>777600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1939500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2061200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1974700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1668600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1781900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1975000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1593800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1351000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1070200</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2662400</v>
+        <v>3111300</v>
       </c>
       <c r="E58" s="3">
+        <v>2689000</v>
+      </c>
+      <c r="F58" s="3">
         <v>3793100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5439700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5349600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3666200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4222100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4469500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5711100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4606400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4679200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5032900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4262500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5504700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6219800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5823500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5678800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4686200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5012900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6203400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>6370700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4814200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5658900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5758300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5769000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>5478000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>5232100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3509800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2952200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2341000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5206000</v>
+        <v>5129300</v>
       </c>
       <c r="E59" s="3">
+        <v>3182200</v>
+      </c>
+      <c r="F59" s="3">
         <v>5165600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4595800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3380500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2468000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4218100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3934500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3498100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2960000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2825500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2745400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2588300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2807600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2900100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2988800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2765800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2811600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2909400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2944500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3547900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4160400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3692600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3668900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3135500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3203500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2823300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2821200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2478900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2698200</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10580400</v>
+      </c>
+      <c r="E60" s="3">
         <v>10139600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11467200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12676100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12022300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10211800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10930800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10434900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10852400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8633500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8525600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8716000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7430900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9143400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10129200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9747200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9136800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8125000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8960400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9807800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10696100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10914200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11412700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11401800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10573100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10463400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>10030300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7924800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6782200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6049400</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2780700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2835300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2804000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2831900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1268100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2760700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2760900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2782700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2030900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1857700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2408800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2419200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2803300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1531700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1690700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3228700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3251200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3162300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4710800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4136000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3674500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3082200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3172000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3311200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3721600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3673100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3785000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4291800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4171300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4192500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E62" s="3">
         <v>40600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>38500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>35600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>45100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>45000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>49600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>42700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>38300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>600000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>581900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>591100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>555800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>565000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>571400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>624300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>649400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>639600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>627800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>635000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>725400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>726500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>698100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>683800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>748700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>633900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>618100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>649800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>592000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>608800</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13887700</v>
+      </c>
+      <c r="E66" s="3">
         <v>13576900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14851100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16022100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13835200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13557000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14239500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13763200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13428900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11194900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11614800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11828700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10895200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11347700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12518600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13733100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13169000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12095800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14527600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14878300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15631500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15259700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15770800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15766100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15412600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15077400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14757400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13139500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>11814400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>11105900</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>16</v>
+      <c r="E72" s="3">
+        <v>6568600</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H72" s="3">
         <v>4873600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4354600</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M72" s="3">
         <v>2954900</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q72" s="3">
         <v>2700400</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U72" s="3">
         <v>2798900</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y72" s="3">
         <v>3697600</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA72" s="3">
         <v>3152900</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC72" s="3">
         <v>2498900</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF72" s="3">
         <v>2379000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2227000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20118000</v>
+      </c>
+      <c r="E76" s="3">
         <v>19529800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19836500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17958100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17696000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17231100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16832600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16222300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16908800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15829700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15229400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15228500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15038700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15144200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15156500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15692600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14314900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13969300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14415400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14371900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15400100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16319000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15499900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14067500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13981000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13191100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12744800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12778800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12459700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12172300</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>589400</v>
+      </c>
+      <c r="E81" s="3">
         <v>295500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>964400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>527500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>597200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>182900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>632500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>87000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>491300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>290000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>36800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-136600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-115200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-117000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-92000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>247800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>139800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>230400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-70100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-844500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>316800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>122100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-61600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>701700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-181000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-165400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>341600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>152100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,13 +7003,14 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>16</v>
+      <c r="D83" s="3">
+        <v>32000</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>16</v>
@@ -6819,12 +7018,12 @@
       <c r="F83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" s="3">
         <v>36700</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>16</v>
       </c>
@@ -6834,8 +7033,8 @@
       <c r="K83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -6867,15 +7066,15 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y83" s="3">
         <v>172900</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
       <c r="Z83" s="3">
         <v>0</v>
       </c>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,8 +7571,11 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7371,24 +7588,24 @@
       <c r="F89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H89" s="3">
         <v>339700</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L89" s="3">
         <v>462200</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
@@ -7419,15 +7636,15 @@
       <c r="V89" s="3">
         <v>0</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y89" s="3">
         <v>1156900</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
         <v>0</v>
       </c>
@@ -7449,8 +7666,11 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7703,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7497,24 +7718,24 @@
       <c r="F91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H91" s="3">
         <v>-16900</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L91" s="3">
         <v>-16200</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -7545,15 +7766,15 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-129800</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,8 +7986,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7773,24 +8003,24 @@
       <c r="F94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H94" s="3">
         <v>-602600</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L94" s="3">
         <v>334200</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
@@ -7821,15 +8051,15 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-380700</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
@@ -7851,8 +8081,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7914,8 +8148,8 @@
       <c r="K96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,8 +8496,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8267,24 +8513,24 @@
       <c r="F100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" s="3">
         <v>328100</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L100" s="3">
         <v>946400</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -8315,15 +8561,15 @@
       <c r="V100" s="3">
         <v>0</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-1460200</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
@@ -8345,13 +8591,16 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>16</v>
+      <c r="D101" s="3">
+        <v>44200</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>16</v>
@@ -8359,12 +8608,12 @@
       <c r="F101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" s="3">
         <v>17000</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>16</v>
       </c>
@@ -8374,8 +8623,8 @@
       <c r="K101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8407,15 +8656,15 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y101" s="3">
         <v>48700</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
@@ -8437,8 +8686,11 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8452,11 +8704,11 @@
         <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>109400</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
@@ -8464,11 +8716,11 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>1759900</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
@@ -8499,15 +8751,15 @@
       <c r="V102" s="3">
         <v>0</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-635300</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
         <v>0</v>
       </c>
@@ -8527,6 +8779,9 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TCOM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TCOM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>TCOM</t>
   </si>
@@ -664,7 +664,7 @@
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -797,17 +797,17 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>1905900</v>
+      <c r="D8" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E8" s="3">
         <v>1746000</v>
       </c>
-      <c r="F8" s="3">
-        <v>2262900</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1757600</v>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H8" s="3">
         <v>1648800</v>
@@ -892,17 +892,17 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>372800</v>
+      <c r="D9" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E9" s="3">
         <v>361700</v>
       </c>
-      <c r="F9" s="3">
-        <v>399200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>318200</v>
+      <c r="F9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H9" s="3">
         <v>310000</v>
@@ -987,17 +987,17 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>1533100</v>
+      <c r="D10" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E10" s="3">
         <v>1384300</v>
       </c>
-      <c r="F10" s="3">
-        <v>1863700</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1439400</v>
+      <c r="F10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H10" s="3">
         <v>1338800</v>
@@ -1117,17 +1117,17 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>485800</v>
+      <c r="D12" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E12" s="3">
         <v>465400</v>
       </c>
-      <c r="F12" s="3">
-        <v>518900</v>
-      </c>
-      <c r="G12" s="3">
-        <v>411900</v>
+      <c r="F12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H12" s="3">
         <v>430600</v>
@@ -1307,17 +1307,17 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>-72500</v>
+      <c r="D14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="3">
         <v>-32700</v>
       </c>
-      <c r="F14" s="3">
-        <v>-181900</v>
-      </c>
-      <c r="G14" s="3">
-        <v>59900</v>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H14" s="3">
         <v>-101700</v>
@@ -1403,16 +1403,16 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>29200</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>29000</v>
       </c>
       <c r="F15" s="3">
-        <v>29000</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>28800</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>28900</v>
@@ -1529,17 +1529,17 @@
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3">
-        <v>1414900</v>
+      <c r="D17" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E17" s="3">
         <v>1430700</v>
       </c>
-      <c r="F17" s="3">
-        <v>1549200</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1268400</v>
+      <c r="F17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H17" s="3">
         <v>1189700</v>
@@ -1624,17 +1624,17 @@
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3">
-        <v>491000</v>
+      <c r="D18" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E18" s="3">
         <v>315200</v>
       </c>
-      <c r="F18" s="3">
-        <v>713700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>489200</v>
+      <c r="F18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H18" s="3">
         <v>459100</v>
@@ -1754,17 +1754,17 @@
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
-        <v>-70100</v>
+      <c r="D20" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E20" s="3">
         <v>25600</v>
       </c>
-      <c r="F20" s="3">
-        <v>-151500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-184500</v>
+      <c r="F20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H20" s="3">
         <v>-117300</v>
@@ -1850,16 +1850,16 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>590400</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
         <v>318700</v>
       </c>
       <c r="F21" s="3">
-        <v>894200</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>702500</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>605400</v>
@@ -1944,17 +1944,17 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>39400</v>
+      <c r="D22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E22" s="3">
         <v>44300</v>
       </c>
-      <c r="F22" s="3">
-        <v>56900</v>
-      </c>
-      <c r="G22" s="3">
-        <v>70700</v>
+      <c r="F22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H22" s="3">
         <v>69100</v>
@@ -2039,17 +2039,17 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>682400</v>
+      <c r="D23" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E23" s="3">
         <v>372200</v>
       </c>
-      <c r="F23" s="3">
-        <v>1075500</v>
-      </c>
-      <c r="G23" s="3">
-        <v>630400</v>
+      <c r="F23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H23" s="3">
         <v>690900</v>
@@ -2134,17 +2134,17 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>87900</v>
+      <c r="D24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E24" s="3">
         <v>72100</v>
       </c>
-      <c r="F24" s="3">
-        <v>102800</v>
-      </c>
-      <c r="G24" s="3">
-        <v>95400</v>
+      <c r="F24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H24" s="3">
         <v>92000</v>
@@ -2324,17 +2324,17 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>594500</v>
+      <c r="D26" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E26" s="3">
         <v>300200</v>
       </c>
-      <c r="F26" s="3">
-        <v>972700</v>
-      </c>
-      <c r="G26" s="3">
-        <v>535000</v>
+      <c r="F26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H26" s="3">
         <v>599000</v>
@@ -2419,17 +2419,17 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>589400</v>
+      <c r="D27" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E27" s="3">
         <v>295500</v>
       </c>
-      <c r="F27" s="3">
-        <v>964400</v>
-      </c>
-      <c r="G27" s="3">
-        <v>527500</v>
+      <c r="F27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H27" s="3">
         <v>597200</v>
@@ -2894,17 +2894,17 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>70100</v>
+      <c r="D32" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E32" s="3">
         <v>-25600</v>
       </c>
-      <c r="F32" s="3">
-        <v>151500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>184500</v>
+      <c r="F32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H32" s="3">
         <v>117300</v>
@@ -2989,17 +2989,17 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>589400</v>
+      <c r="D33" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E33" s="3">
         <v>295500</v>
       </c>
-      <c r="F33" s="3">
-        <v>964400</v>
-      </c>
-      <c r="G33" s="3">
-        <v>527500</v>
+      <c r="F33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H33" s="3">
         <v>597200</v>
@@ -3179,17 +3179,17 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>589400</v>
+      <c r="D35" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E35" s="3">
         <v>295500</v>
       </c>
-      <c r="F35" s="3">
-        <v>964400</v>
-      </c>
-      <c r="G35" s="3">
-        <v>527500</v>
+      <c r="F35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H35" s="3">
         <v>597200</v>
@@ -3444,17 +3444,17 @@
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>7766800</v>
+      <c r="D41" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E41" s="3">
         <v>6636300</v>
       </c>
-      <c r="F41" s="3">
-        <v>5985000</v>
-      </c>
-      <c r="G41" s="3">
-        <v>7094200</v>
+      <c r="F41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H41" s="3">
         <v>5842700</v>
@@ -3540,16 +3540,16 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2995800</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>3901200</v>
       </c>
       <c r="F42" s="3">
-        <v>4892200</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>5258900</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>3532600</v>
@@ -3634,17 +3634,17 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>1840700</v>
+      <c r="D43" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E43" s="3">
         <v>2992400</v>
       </c>
-      <c r="F43" s="3">
-        <v>1972900</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1776100</v>
+      <c r="F43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H43" s="3">
         <v>2119800</v>
@@ -3824,17 +3824,17 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>2870800</v>
+      <c r="D45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E45" s="3">
         <v>1444000</v>
       </c>
-      <c r="F45" s="3">
-        <v>3487200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2595700</v>
+      <c r="F45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H45" s="3">
         <v>2000000</v>
@@ -3919,17 +3919,17 @@
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>15474100</v>
+      <c r="D46" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E46" s="3">
         <v>15360800</v>
       </c>
-      <c r="F46" s="3">
-        <v>16337300</v>
-      </c>
-      <c r="G46" s="3">
-        <v>16725000</v>
+      <c r="F46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H46" s="3">
         <v>13853200</v>
@@ -4014,17 +4014,17 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>7141900</v>
+      <c r="D47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E47" s="3">
         <v>6465700</v>
       </c>
-      <c r="F47" s="3">
-        <v>6664100</v>
-      </c>
-      <c r="G47" s="3">
-        <v>6246400</v>
+      <c r="F47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H47" s="3">
         <v>6602300</v>
@@ -4109,17 +4109,17 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>800900</v>
+      <c r="D48" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E48" s="3">
         <v>795700</v>
       </c>
-      <c r="F48" s="3">
-        <v>825700</v>
-      </c>
-      <c r="G48" s="3">
-        <v>801400</v>
+      <c r="F48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H48" s="3">
         <v>793600</v>
@@ -4204,17 +4204,17 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>10191600</v>
+      <c r="D49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E49" s="3">
         <v>10104100</v>
       </c>
-      <c r="F49" s="3">
-        <v>10524500</v>
-      </c>
-      <c r="G49" s="3">
-        <v>9898600</v>
+      <c r="F49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H49" s="3">
         <v>9967900</v>
@@ -4489,17 +4489,17 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>64800</v>
+      <c r="D52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E52" s="3">
         <v>62200</v>
       </c>
-      <c r="F52" s="3">
-        <v>77700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>74000</v>
+      <c r="F52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H52" s="3">
         <v>86300</v>
@@ -4679,17 +4679,17 @@
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>34143500</v>
+      <c r="D54" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E54" s="3">
         <v>33234400</v>
       </c>
-      <c r="F54" s="3">
-        <v>34827900</v>
-      </c>
-      <c r="G54" s="3">
-        <v>34103000</v>
+      <c r="F54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H54" s="3">
         <v>31646800</v>
@@ -4844,17 +4844,17 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>2339800</v>
+      <c r="D57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E57" s="3">
         <v>2325600</v>
       </c>
-      <c r="F57" s="3">
-        <v>2508500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2640600</v>
+      <c r="F57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H57" s="3">
         <v>2490800</v>
@@ -4939,17 +4939,17 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>3111300</v>
+      <c r="D58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E58" s="3">
         <v>2689000</v>
       </c>
-      <c r="F58" s="3">
-        <v>3793100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>5439700</v>
+      <c r="F58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H58" s="3">
         <v>5349600</v>
@@ -5034,17 +5034,17 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>5129300</v>
+      <c r="D59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E59" s="3">
         <v>3182200</v>
       </c>
-      <c r="F59" s="3">
-        <v>5165600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>4595800</v>
+      <c r="F59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H59" s="3">
         <v>3380500</v>
@@ -5129,17 +5129,17 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>10580400</v>
+      <c r="D60" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E60" s="3">
         <v>10139600</v>
       </c>
-      <c r="F60" s="3">
-        <v>11467200</v>
-      </c>
-      <c r="G60" s="3">
-        <v>12676100</v>
+      <c r="F60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H60" s="3">
         <v>12022300</v>
@@ -5225,16 +5225,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2780700</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
         <v>2835300</v>
       </c>
       <c r="F61" s="3">
-        <v>2804000</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>2831900</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>1268100</v>
@@ -5319,17 +5319,17 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>45100</v>
+      <c r="D62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E62" s="3">
         <v>40600</v>
       </c>
-      <c r="F62" s="3">
-        <v>38500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>35600</v>
+      <c r="F62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H62" s="3">
         <v>45100</v>
@@ -5699,17 +5699,17 @@
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>13887700</v>
+      <c r="D66" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E66" s="3">
         <v>13576900</v>
       </c>
-      <c r="F66" s="3">
-        <v>14851100</v>
-      </c>
-      <c r="G66" s="3">
-        <v>16022100</v>
+      <c r="F66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H66" s="3">
         <v>13835200</v>
@@ -6589,17 +6589,17 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>20118000</v>
+      <c r="D76" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E76" s="3">
         <v>19529800</v>
       </c>
-      <c r="F76" s="3">
-        <v>19836500</v>
-      </c>
-      <c r="G76" s="3">
-        <v>17958100</v>
+      <c r="F76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H76" s="3">
         <v>17696000</v>
@@ -6879,17 +6879,17 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>589400</v>
+      <c r="D81" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E81" s="3">
         <v>295500</v>
       </c>
-      <c r="F81" s="3">
-        <v>964400</v>
-      </c>
-      <c r="G81" s="3">
-        <v>527500</v>
+      <c r="F81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H81" s="3">
         <v>597200</v>
